--- a/risk/Risk_Analysis_T3_5yrs_Present_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_5yrs_Present_Perfect.xlsx
@@ -25,18 +25,12 @@
     <sheet name="Kashmore_Exp" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="Kashmore_Vul" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="Kashmore_Dmg" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Naushahro Feroze_Exp" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Naushahro Feroze_Vul" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Naushahro Feroze_Dmg" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Qambar Shahdadkot_Exp" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Qambar Shahdadkot_Vul" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Qambar Shahdadkot_Dmg" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Shaheed Benazirabad_Exp" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Shaheed Benazirabad_Vul" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Shaheed Benazirabad_Dmg" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Shikarpur_Exp" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Shikarpur_Vul" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Shikarpur_Dmg" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Qambar Shahdadkot_Exp" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Qambar Shahdadkot_Vul" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Qambar Shahdadkot_Dmg" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Shikarpur_Exp" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Shikarpur_Vul" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Shikarpur_Dmg" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9772,7 +9766,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Exp</t>
+          <t>Region: Qambar Shahdadkot | Mode: Exp</t>
         </is>
       </c>
     </row>
@@ -9843,37 +9837,37 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>2259</v>
+        <v>24485.85</v>
       </c>
       <c r="C4" t="n">
-        <v>407736</v>
+        <v>2743272</v>
       </c>
       <c r="D4" t="n">
-        <v>320364</v>
+        <v>2155428</v>
       </c>
       <c r="E4" t="n">
-        <v>63000</v>
+        <v>432000</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G4" t="n">
-        <v>4530</v>
+        <v>60330</v>
       </c>
       <c r="H4" t="n">
-        <v>120</v>
+        <v>10200</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>16950</v>
+        <v>164250</v>
       </c>
     </row>
     <row r="5">
@@ -9881,37 +9875,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3014.19</v>
+        <v>4877.55</v>
       </c>
       <c r="C5" t="n">
-        <v>417312</v>
+        <v>411768</v>
       </c>
       <c r="D5" t="n">
-        <v>327888</v>
+        <v>323532</v>
       </c>
       <c r="E5" t="n">
-        <v>52200</v>
+        <v>37800</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>6360</v>
+        <v>14100</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1170</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>15930</v>
+        <v>54630</v>
       </c>
     </row>
     <row r="6">
@@ -9919,25 +9913,25 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>3124.8</v>
+        <v>1440.45</v>
       </c>
       <c r="C6" t="n">
-        <v>255024</v>
+        <v>66528</v>
       </c>
       <c r="D6" t="n">
-        <v>200376</v>
+        <v>52272</v>
       </c>
       <c r="E6" t="n">
-        <v>26100</v>
+        <v>1800</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>5580</v>
+        <v>1440</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -9949,7 +9943,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>9600</v>
+        <v>15180</v>
       </c>
     </row>
     <row r="7">
@@ -9957,22 +9951,22 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>2237.67</v>
+        <v>204.21</v>
       </c>
       <c r="C7" t="n">
-        <v>140616</v>
+        <v>6552</v>
       </c>
       <c r="D7" t="n">
-        <v>110484</v>
+        <v>5148</v>
       </c>
       <c r="E7" t="n">
-        <v>7200</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>4050</v>
+        <v>600</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -9987,7 +9981,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>6030</v>
+        <v>6840</v>
       </c>
     </row>
     <row r="8">
@@ -9995,22 +9989,22 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1246.59</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>52416</v>
+        <v>6048</v>
       </c>
       <c r="D8" t="n">
-        <v>41184</v>
+        <v>4752</v>
       </c>
       <c r="E8" t="n">
-        <v>5400</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1410</v>
+        <v>3810</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -10025,7 +10019,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3360</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="9">
@@ -10033,25 +10027,25 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>613.89</v>
+        <v>66.33</v>
       </c>
       <c r="C9" t="n">
-        <v>17640</v>
+        <v>504</v>
       </c>
       <c r="D9" t="n">
-        <v>13860</v>
+        <v>396</v>
       </c>
       <c r="E9" t="n">
-        <v>7200</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>840</v>
+        <v>150</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -10063,7 +10057,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>510</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="10">
@@ -10071,13 +10065,13 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>381.06</v>
+        <v>26.19</v>
       </c>
       <c r="C10" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1584</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -10086,7 +10080,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>390</v>
+        <v>30</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -10101,7 +10095,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>450</v>
+        <v>960</v>
       </c>
     </row>
     <row r="11">
@@ -10109,13 +10103,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>215.46</v>
+        <v>7.83</v>
       </c>
       <c r="C11" t="n">
-        <v>3024</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>2376</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -10124,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -10139,7 +10133,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>300</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12">
@@ -10147,13 +10141,13 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>156.78</v>
+        <v>3.42</v>
       </c>
       <c r="C12" t="n">
-        <v>1008</v>
+        <v>504</v>
       </c>
       <c r="D12" t="n">
-        <v>792</v>
+        <v>396</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -10162,7 +10156,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -10177,7 +10171,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -10185,7 +10179,7 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>168.84</v>
+        <v>0.72</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -10200,7 +10194,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -10215,7 +10209,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
@@ -10223,13 +10217,13 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>42.84</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -10238,7 +10232,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -10253,7 +10247,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>540</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -10261,13 +10255,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -10299,7 +10293,7 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -10337,7 +10331,7 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -10375,7 +10369,7 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -10413,7 +10407,7 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -11636,7 +11630,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Vul</t>
+          <t>Region: Qambar Shahdadkot | Mode: Vul</t>
         </is>
       </c>
     </row>
@@ -11745,16 +11739,16 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>1356.39</v>
+        <v>2194.9</v>
       </c>
       <c r="C5" t="n">
-        <v>229521.6</v>
+        <v>226472.4</v>
       </c>
       <c r="D5" t="n">
-        <v>108530.93</v>
+        <v>107089.09</v>
       </c>
       <c r="E5" t="n">
-        <v>5757.66</v>
+        <v>4169.34</v>
       </c>
       <c r="F5" t="n">
         <v>0.06</v>
@@ -11763,19 +11757,19 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>421.2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>3345.3</v>
+        <v>11472.3</v>
       </c>
     </row>
     <row r="6">
@@ -11783,25 +11777,25 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>2499.84</v>
+        <v>1152.36</v>
       </c>
       <c r="C6" t="n">
-        <v>229521.6</v>
+        <v>59875.2</v>
       </c>
       <c r="D6" t="n">
-        <v>101590.63</v>
+        <v>26501.9</v>
       </c>
       <c r="E6" t="n">
-        <v>4410.9</v>
+        <v>304.2</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>279</v>
+        <v>72</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>34.2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -11813,7 +11807,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>3552</v>
+        <v>5616.6</v>
       </c>
     </row>
     <row r="7">
@@ -11821,22 +11815,22 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>2125.79</v>
+        <v>194</v>
       </c>
       <c r="C7" t="n">
-        <v>140616</v>
+        <v>6552</v>
       </c>
       <c r="D7" t="n">
-        <v>70488.78999999999</v>
+        <v>3284.42</v>
       </c>
       <c r="E7" t="n">
-        <v>1531.44</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>607.5</v>
+        <v>90</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -11851,7 +11845,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3618</v>
+        <v>4104</v>
       </c>
     </row>
     <row r="8">
@@ -11859,22 +11853,22 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1246.59</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>52416</v>
+        <v>6048</v>
       </c>
       <c r="D8" t="n">
-        <v>30311.42</v>
+        <v>3497.47</v>
       </c>
       <c r="E8" t="n">
-        <v>1324.62</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>916.5</v>
+        <v>2476.5</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -11889,7 +11883,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2385.6</v>
+        <v>2215.2</v>
       </c>
     </row>
     <row r="9">
@@ -11897,25 +11891,25 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>613.89</v>
+        <v>66.33</v>
       </c>
       <c r="C9" t="n">
-        <v>17640</v>
+        <v>504</v>
       </c>
       <c r="D9" t="n">
-        <v>11129.58</v>
+        <v>317.99</v>
       </c>
       <c r="E9" t="n">
-        <v>1927.44</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>714</v>
+        <v>127.5</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -11927,7 +11921,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>413.1</v>
+        <v>1871.1</v>
       </c>
     </row>
     <row r="10">
@@ -11935,13 +11929,13 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>381.06</v>
+        <v>26.19</v>
       </c>
       <c r="C10" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1378.08</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -11950,7 +11944,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>390</v>
+        <v>30</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -11965,7 +11959,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>400.5</v>
+        <v>854.4</v>
       </c>
     </row>
     <row r="11">
@@ -11973,13 +11967,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>215.46</v>
+        <v>7.83</v>
       </c>
       <c r="C11" t="n">
-        <v>3024</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>2134.84</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -11988,7 +11982,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -12003,7 +11997,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>300</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12">
@@ -12011,13 +12005,13 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>156.78</v>
+        <v>3.42</v>
       </c>
       <c r="C12" t="n">
-        <v>1008</v>
+        <v>504</v>
       </c>
       <c r="D12" t="n">
-        <v>734.1799999999999</v>
+        <v>367.09</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -12026,7 +12020,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12041,7 +12035,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -12049,7 +12043,7 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>168.84</v>
+        <v>0.72</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -12064,7 +12058,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -12079,7 +12073,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
@@ -12087,13 +12081,13 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>42.84</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>384.91</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -12102,7 +12096,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -12117,7 +12111,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>540</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -12125,13 +12119,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>390.46</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -12163,7 +12157,7 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -12201,7 +12195,7 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -12239,7 +12233,7 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -12277,7 +12271,7 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -12568,7 +12562,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Dmg</t>
+          <t>Region: Qambar Shahdadkot | Mode: Dmg</t>
         </is>
       </c>
     </row>
@@ -12677,16 +12671,16 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>2984048.1</v>
+        <v>4828774.5</v>
       </c>
       <c r="C5" t="n">
-        <v>12623688</v>
+        <v>12455982</v>
       </c>
       <c r="D5" t="n">
-        <v>10997438.93</v>
+        <v>10851337.69</v>
       </c>
       <c r="E5" t="n">
-        <v>1060791.28</v>
+        <v>768159.2</v>
       </c>
       <c r="F5" t="n">
         <v>2500.02</v>
@@ -12695,19 +12689,19 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>116524.98</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>17499.9</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>31512.73</v>
+        <v>108069.07</v>
       </c>
     </row>
     <row r="6">
@@ -12715,25 +12709,25 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>5499648</v>
+        <v>2535192</v>
       </c>
       <c r="C6" t="n">
-        <v>12623688</v>
+        <v>3293136</v>
       </c>
       <c r="D6" t="n">
-        <v>10294178.74</v>
+        <v>2685437.93</v>
       </c>
       <c r="E6" t="n">
-        <v>812664.22</v>
+        <v>56045.81</v>
       </c>
       <c r="F6" t="n">
-        <v>12500.1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>5161.5</v>
+        <v>1332</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>9461.43</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -12745,7 +12739,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>33459.84</v>
+        <v>52908.37</v>
       </c>
     </row>
     <row r="7">
@@ -12753,22 +12747,22 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>4676730.3</v>
+        <v>426798.9</v>
       </c>
       <c r="C7" t="n">
-        <v>7733880</v>
+        <v>360360</v>
       </c>
       <c r="D7" t="n">
-        <v>7142629.29</v>
+        <v>332810.68</v>
       </c>
       <c r="E7" t="n">
-        <v>282152.51</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>25000.2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>11238.75</v>
+        <v>1665</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -12783,7 +12777,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>34081.56</v>
+        <v>38659.68</v>
       </c>
     </row>
     <row r="8">
@@ -12791,22 +12785,22 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>2742498</v>
+        <v>208296</v>
       </c>
       <c r="C8" t="n">
-        <v>2882880</v>
+        <v>332640</v>
       </c>
       <c r="D8" t="n">
-        <v>3071456.59</v>
+        <v>354398.84</v>
       </c>
       <c r="E8" t="n">
-        <v>244047.99</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>16955.25</v>
+        <v>45815.25</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -12821,7 +12815,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>22472.35</v>
+        <v>20867.18</v>
       </c>
     </row>
     <row r="9">
@@ -12829,25 +12823,25 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>1350558</v>
+        <v>145926</v>
       </c>
       <c r="C9" t="n">
-        <v>970200</v>
+        <v>27720</v>
       </c>
       <c r="D9" t="n">
-        <v>1127760.34</v>
+        <v>32221.72</v>
       </c>
       <c r="E9" t="n">
-        <v>355111.55</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>41667</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>13209</v>
+        <v>2358.75</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>8299.5</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -12859,7 +12853,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>3891.4</v>
+        <v>17625.76</v>
       </c>
     </row>
     <row r="10">
@@ -12867,13 +12861,13 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>838332</v>
+        <v>57618</v>
       </c>
       <c r="C10" t="n">
-        <v>110880</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>139640.85</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -12882,7 +12876,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>7215</v>
+        <v>555</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -12897,7 +12891,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3772.71</v>
+        <v>8048.45</v>
       </c>
     </row>
     <row r="11">
@@ -12905,13 +12899,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>474012</v>
+        <v>17226</v>
       </c>
       <c r="C11" t="n">
-        <v>166320</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>216322.93</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -12920,7 +12914,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2220</v>
+        <v>555</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -12935,7 +12929,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2826</v>
+        <v>1695.6</v>
       </c>
     </row>
     <row r="12">
@@ -12943,13 +12937,13 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>344916</v>
+        <v>7524</v>
       </c>
       <c r="C12" t="n">
-        <v>55440</v>
+        <v>27720</v>
       </c>
       <c r="D12" t="n">
-        <v>74394.86</v>
+        <v>37197.43</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -12958,7 +12952,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2220</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12973,7 +12967,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>847.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -12981,7 +12975,7 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>371448</v>
+        <v>1584</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -12996,7 +12990,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>2775</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13011,7 +13005,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1413</v>
+        <v>282.6</v>
       </c>
     </row>
     <row r="14">
@@ -13019,13 +13013,13 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>94248</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>27720</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>39003.13</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -13034,7 +13028,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>7770</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13049,7 +13043,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>5086.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -13057,13 +13051,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>9504</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>39564.91</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13095,7 +13089,7 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>2178</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -13133,7 +13127,7 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -13171,7 +13165,7 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -13209,7 +13203,7 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -13500,7 +13494,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Exp</t>
+          <t>Region: Shikarpur | Mode: Exp</t>
         </is>
       </c>
     </row>
@@ -13571,37 +13565,37 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>24485.85</v>
+        <v>6770.52</v>
       </c>
       <c r="C4" t="n">
-        <v>2743272</v>
+        <v>701064</v>
       </c>
       <c r="D4" t="n">
-        <v>2155428</v>
+        <v>550836</v>
       </c>
       <c r="E4" t="n">
-        <v>432000</v>
+        <v>239400</v>
       </c>
       <c r="F4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>60330</v>
+        <v>19770</v>
       </c>
       <c r="H4" t="n">
-        <v>10200</v>
+        <v>2100</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>164250</v>
+        <v>89100</v>
       </c>
     </row>
     <row r="5">
@@ -13609,37 +13603,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>4877.55</v>
+        <v>589.23</v>
       </c>
       <c r="C5" t="n">
-        <v>411768</v>
+        <v>61992</v>
       </c>
       <c r="D5" t="n">
-        <v>323532</v>
+        <v>48708</v>
       </c>
       <c r="E5" t="n">
-        <v>37800</v>
+        <v>18000</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>14100</v>
+        <v>1830</v>
       </c>
       <c r="H5" t="n">
-        <v>1170</v>
+        <v>90</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>54630</v>
+        <v>13440</v>
       </c>
     </row>
     <row r="6">
@@ -13647,25 +13641,25 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>1440.45</v>
+        <v>66.87</v>
       </c>
       <c r="C6" t="n">
-        <v>66528</v>
+        <v>1512</v>
       </c>
       <c r="D6" t="n">
-        <v>52272</v>
+        <v>1188</v>
       </c>
       <c r="E6" t="n">
-        <v>1800</v>
+        <v>900</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1440</v>
+        <v>180</v>
       </c>
       <c r="H6" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -13677,7 +13671,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>15180</v>
+        <v>720</v>
       </c>
     </row>
     <row r="7">
@@ -13685,13 +13679,13 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>204.21</v>
+        <v>2.43</v>
       </c>
       <c r="C7" t="n">
-        <v>6552</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>5148</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -13700,7 +13694,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>600</v>
+        <v>30</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -13715,7 +13709,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>6840</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8">
@@ -13723,13 +13717,13 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>94.68000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="C8" t="n">
-        <v>6048</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>4752</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -13738,7 +13732,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>3810</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -13753,7 +13747,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3120</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9">
@@ -13761,13 +13755,13 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>66.33</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -13776,10 +13770,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -13791,7 +13785,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2310</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -13799,7 +13793,7 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>26.19</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -13814,7 +13808,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -13829,7 +13823,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>960</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -13837,7 +13831,7 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>7.83</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -13852,7 +13846,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -13867,7 +13861,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -13875,13 +13869,13 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -13913,7 +13907,7 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -13943,7 +13937,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -13992,10 +13986,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14432,7 +14426,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Vul</t>
+          <t>Region: Shikarpur | Mode: Vul</t>
         </is>
       </c>
     </row>
@@ -14541,37 +14535,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>2194.9</v>
+        <v>265.15</v>
       </c>
       <c r="C5" t="n">
-        <v>226472.4</v>
+        <v>34095.6</v>
       </c>
       <c r="D5" t="n">
-        <v>107089.09</v>
+        <v>16122.35</v>
       </c>
       <c r="E5" t="n">
-        <v>4169.34</v>
+        <v>1985.4</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>421.2</v>
+        <v>32.4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>11472.3</v>
+        <v>2822.4</v>
       </c>
     </row>
     <row r="6">
@@ -14579,25 +14573,25 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>1152.36</v>
+        <v>53.5</v>
       </c>
       <c r="C6" t="n">
-        <v>59875.2</v>
+        <v>1360.8</v>
       </c>
       <c r="D6" t="n">
-        <v>26501.9</v>
+        <v>602.3200000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>304.2</v>
+        <v>152.1</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="H6" t="n">
-        <v>34.2</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -14609,7 +14603,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>5616.6</v>
+        <v>266.4</v>
       </c>
     </row>
     <row r="7">
@@ -14617,13 +14611,13 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>194</v>
+        <v>2.31</v>
       </c>
       <c r="C7" t="n">
-        <v>6552</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>3284.42</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -14632,7 +14626,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>90</v>
+        <v>4.5</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -14647,7 +14641,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>4104</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8">
@@ -14655,13 +14649,13 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>94.68000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="C8" t="n">
-        <v>6048</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>3497.47</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -14670,7 +14664,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2476.5</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -14685,7 +14679,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2215.2</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="9">
@@ -14693,13 +14687,13 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>66.33</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>317.99</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -14708,10 +14702,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>127.5</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -14723,7 +14717,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1871.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -14731,7 +14725,7 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>26.19</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -14746,7 +14740,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -14761,7 +14755,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>854.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -14769,7 +14763,7 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>7.83</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -14784,7 +14778,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -14799,7 +14793,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -14807,13 +14801,13 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>367.09</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -14845,7 +14839,7 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -14875,7 +14869,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -14924,10 +14918,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>390.46</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -15364,7 +15358,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Dmg</t>
+          <t>Region: Shikarpur | Mode: Dmg</t>
         </is>
       </c>
     </row>
@@ -15473,37 +15467,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>4828774.5</v>
+        <v>583337.7</v>
       </c>
       <c r="C5" t="n">
-        <v>12455982</v>
+        <v>1875258</v>
       </c>
       <c r="D5" t="n">
-        <v>10851337.69</v>
+        <v>1633677.52</v>
       </c>
       <c r="E5" t="n">
-        <v>768159.2</v>
+        <v>365790.1</v>
       </c>
       <c r="F5" t="n">
-        <v>2500.02</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>116524.98</v>
+        <v>8963.459999999999</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>17499.9</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>108069.07</v>
+        <v>26587.01</v>
       </c>
     </row>
     <row r="6">
@@ -15511,25 +15505,25 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>2535192</v>
+        <v>117691.2</v>
       </c>
       <c r="C6" t="n">
-        <v>3293136</v>
+        <v>74844</v>
       </c>
       <c r="D6" t="n">
-        <v>2685437.93</v>
+        <v>61032.68</v>
       </c>
       <c r="E6" t="n">
-        <v>56045.81</v>
+        <v>28022.9</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1332</v>
+        <v>166.5</v>
       </c>
       <c r="H6" t="n">
-        <v>9461.43</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -15541,7 +15535,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>52908.37</v>
+        <v>2509.49</v>
       </c>
     </row>
     <row r="7">
@@ -15549,13 +15543,13 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>426798.9</v>
+        <v>5078.7</v>
       </c>
       <c r="C7" t="n">
-        <v>360360</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>332810.68</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -15564,7 +15558,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1665</v>
+        <v>83.25</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -15579,7 +15573,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>38659.68</v>
+        <v>678.24</v>
       </c>
     </row>
     <row r="8">
@@ -15587,13 +15581,13 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>208296</v>
+        <v>396</v>
       </c>
       <c r="C8" t="n">
-        <v>332640</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>354398.84</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -15602,7 +15596,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>45815.25</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -15617,4667 +15611,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>20867.18</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>145926</v>
-      </c>
-      <c r="C9" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D9" t="n">
-        <v>32221.72</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2358.75</v>
-      </c>
-      <c r="H9" t="n">
-        <v>8299.5</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>17625.76</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>57618</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>555</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>8048.45</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>17226</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>555</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1695.6</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>7524</v>
-      </c>
-      <c r="C12" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D12" t="n">
-        <v>37197.43</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>1584</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>282.6</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D15" t="n">
-        <v>39564.91</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>3006.63</v>
-      </c>
-      <c r="C4" t="n">
-        <v>357336</v>
-      </c>
-      <c r="D4" t="n">
-        <v>280764</v>
-      </c>
-      <c r="E4" t="n">
-        <v>97200</v>
-      </c>
-      <c r="F4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G4" t="n">
-        <v>3960</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1350</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>12450</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>3993.66</v>
-      </c>
-      <c r="C5" t="n">
-        <v>315000</v>
-      </c>
-      <c r="D5" t="n">
-        <v>247500</v>
-      </c>
-      <c r="E5" t="n">
-        <v>58500</v>
-      </c>
-      <c r="F5" t="n">
-        <v>3</v>
-      </c>
-      <c r="G5" t="n">
-        <v>3990</v>
-      </c>
-      <c r="H5" t="n">
-        <v>240</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>8040</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>4223.88</v>
-      </c>
-      <c r="C6" t="n">
-        <v>238392</v>
-      </c>
-      <c r="D6" t="n">
-        <v>187308</v>
-      </c>
-      <c r="E6" t="n">
-        <v>45000</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>3900</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>8100</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>3414.06</v>
-      </c>
-      <c r="C7" t="n">
-        <v>162288</v>
-      </c>
-      <c r="D7" t="n">
-        <v>127512</v>
-      </c>
-      <c r="E7" t="n">
-        <v>18000</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>3180</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>10620</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>2475.18</v>
-      </c>
-      <c r="C8" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D8" t="n">
-        <v>43560</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2700</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2070</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>4560</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>1693.08</v>
-      </c>
-      <c r="C9" t="n">
-        <v>28224</v>
-      </c>
-      <c r="D9" t="n">
-        <v>22176</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>300</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>884.52</v>
-      </c>
-      <c r="C10" t="n">
-        <v>5544</v>
-      </c>
-      <c r="D10" t="n">
-        <v>4356</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>240</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>527.67</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3528</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2772</v>
-      </c>
-      <c r="E11" t="n">
-        <v>900</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>397.62</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>367.02</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2016</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1584</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>491.13</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D14" t="n">
-        <v>792</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>244.89</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>42.66</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>27.18</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Vul</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>1797.15</v>
-      </c>
-      <c r="C5" t="n">
-        <v>173250</v>
-      </c>
-      <c r="D5" t="n">
-        <v>81922.5</v>
-      </c>
-      <c r="E5" t="n">
-        <v>6452.55</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>86.40000000000001</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1688.4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>3379.1</v>
-      </c>
-      <c r="C6" t="n">
-        <v>214552.8</v>
-      </c>
-      <c r="D6" t="n">
-        <v>94965.16</v>
-      </c>
-      <c r="E6" t="n">
-        <v>7605</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>195</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2997</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>3243.36</v>
-      </c>
-      <c r="C7" t="n">
-        <v>162288</v>
-      </c>
-      <c r="D7" t="n">
-        <v>81352.66</v>
-      </c>
-      <c r="E7" t="n">
-        <v>3828.6</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G7" t="n">
-        <v>477</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>6372</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>2475.18</v>
-      </c>
-      <c r="C8" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D8" t="n">
-        <v>32060.16</v>
-      </c>
-      <c r="E8" t="n">
-        <v>662.3099999999999</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1345.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3237.6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>1693.08</v>
-      </c>
-      <c r="C9" t="n">
-        <v>28224</v>
-      </c>
-      <c r="D9" t="n">
-        <v>17807.33</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>255</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>631.8</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>884.52</v>
-      </c>
-      <c r="C10" t="n">
-        <v>5544</v>
-      </c>
-      <c r="D10" t="n">
-        <v>3789.72</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>240</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>186.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>527.67</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3528</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2490.64</v>
-      </c>
-      <c r="E11" t="n">
-        <v>368.82</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>397.62</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1101.28</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>367.02</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2016</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1504.01</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>491.13</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D14" t="n">
-        <v>769.8200000000001</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>244.89</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1171.37</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>42.66</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>27.18</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Dmg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>3953723.4</v>
-      </c>
-      <c r="C5" t="n">
-        <v>9528750</v>
-      </c>
-      <c r="D5" t="n">
-        <v>8301206.92</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1188817.81</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2500.02</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>23902.56</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>15904.73</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>7434028.8</v>
-      </c>
-      <c r="C6" t="n">
-        <v>11800404</v>
-      </c>
-      <c r="D6" t="n">
-        <v>9622819.26</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1401145.2</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>3607.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>28231.74</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>7135385.4</v>
-      </c>
-      <c r="C7" t="n">
-        <v>8925840</v>
-      </c>
-      <c r="D7" t="n">
-        <v>8243464.63</v>
-      </c>
-      <c r="E7" t="n">
-        <v>705381.26</v>
-      </c>
-      <c r="F7" t="n">
-        <v>25000.2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>8824.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>60024.24</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>5445396</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3049200</v>
-      </c>
-      <c r="D8" t="n">
-        <v>3248656.01</v>
-      </c>
-      <c r="E8" t="n">
-        <v>122023.99</v>
-      </c>
-      <c r="F8" t="n">
-        <v>39583.65</v>
-      </c>
-      <c r="G8" t="n">
-        <v>24891.75</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>30498.19</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>3724776</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1552320</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1804416.55</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4717.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>5951.56</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>1945944</v>
-      </c>
-      <c r="C10" t="n">
-        <v>304920</v>
-      </c>
-      <c r="D10" t="n">
-        <v>384012.33</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>4440</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1760.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>1160874</v>
-      </c>
-      <c r="C11" t="n">
-        <v>194040</v>
-      </c>
-      <c r="D11" t="n">
-        <v>252376.75</v>
-      </c>
-      <c r="E11" t="n">
-        <v>67951.39999999999</v>
-      </c>
-      <c r="F11" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>874764</v>
-      </c>
-      <c r="C12" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D12" t="n">
-        <v>111592.3</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>807444</v>
-      </c>
-      <c r="C13" t="n">
-        <v>110880</v>
-      </c>
-      <c r="D13" t="n">
-        <v>152401.13</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>1080486</v>
-      </c>
-      <c r="C14" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D14" t="n">
-        <v>78006.27</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>538758</v>
-      </c>
-      <c r="C15" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D15" t="n">
-        <v>118694.72</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>93852</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>59796</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>6770.52</v>
-      </c>
-      <c r="C4" t="n">
-        <v>701064</v>
-      </c>
-      <c r="D4" t="n">
-        <v>550836</v>
-      </c>
-      <c r="E4" t="n">
-        <v>239400</v>
-      </c>
-      <c r="F4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G4" t="n">
-        <v>19770</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2100</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>89100</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>589.23</v>
-      </c>
-      <c r="C5" t="n">
-        <v>61992</v>
-      </c>
-      <c r="D5" t="n">
-        <v>48708</v>
-      </c>
-      <c r="E5" t="n">
-        <v>18000</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1830</v>
-      </c>
-      <c r="H5" t="n">
-        <v>90</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>13440</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>66.87</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E6" t="n">
-        <v>900</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>180</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>30</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Vul</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>265.15</v>
-      </c>
-      <c r="C5" t="n">
-        <v>34095.6</v>
-      </c>
-      <c r="D5" t="n">
-        <v>16122.35</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1985.4</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>2822.4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1360.8</v>
-      </c>
-      <c r="D6" t="n">
-        <v>602.3200000000001</v>
-      </c>
-      <c r="E6" t="n">
-        <v>152.1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>9</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>266.4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>106.5</v>
+        <v>1003.23</v>
       </c>
     </row>
     <row r="9">
@@ -21876,938 +17210,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Dmg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>583337.7</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1875258</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1633677.52</v>
-      </c>
-      <c r="E5" t="n">
-        <v>365790.1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>8963.459999999999</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>26587.01</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>117691.2</v>
-      </c>
-      <c r="C6" t="n">
-        <v>74844</v>
-      </c>
-      <c r="D6" t="n">
-        <v>61032.68</v>
-      </c>
-      <c r="E6" t="n">
-        <v>28022.9</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>166.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2509.49</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>5078.7</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>83.25</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>678.24</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>396</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1003.23</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/risk/Risk_Analysis_T3_5yrs_Present_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_5yrs_Present_Perfect.xlsx
@@ -538,7 +538,7 @@
         <v>40230</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
         <v>24</v>
@@ -576,7 +576,7 @@
         <v>6180</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
         <v>2</v>
@@ -1508,7 +1508,7 @@
         <v>1950</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
         <v>702</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -3372,7 +3372,7 @@
         <v>194208.3</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>57499.5</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -9858,7 +9858,7 @@
         <v>10200</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
@@ -9896,7 +9896,7 @@
         <v>1170</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -10828,7 +10828,7 @@
         <v>2224.8</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="J5" t="n">
         <v>0.6</v>
@@ -11760,7 +11760,7 @@
         <v>421.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="J5" t="n">
         <v>0.3</v>
@@ -12692,7 +12692,7 @@
         <v>116524.98</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>57499.5</v>
       </c>
       <c r="J5" t="n">
         <v>17499.9</v>
@@ -16420,7 +16420,7 @@
         <v>615490.92</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>114999</v>
       </c>
       <c r="J5" t="n">
         <v>34999.8</v>
@@ -17314,7 +17314,7 @@
         <v>3180</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>5</v>

--- a/risk/Risk_Analysis_T3_5yrs_Present_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_5yrs_Present_Perfect.xlsx
@@ -544,7 +544,7 @@
         <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>474</v>
       </c>
       <c r="L4" t="n">
         <v>720180</v>
@@ -582,7 +582,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="L5" t="n">
         <v>229740</v>
@@ -620,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="L6" t="n">
         <v>80550</v>
@@ -658,7 +658,7 @@
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L7" t="n">
         <v>42600</v>
@@ -696,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
         <v>17100</v>
@@ -734,7 +734,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L9" t="n">
         <v>5910</v>
@@ -1476,7 +1476,7 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="L4" t="n">
         <v>59670</v>
@@ -1514,7 +1514,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="L5" t="n">
         <v>36300</v>
@@ -1552,7 +1552,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L6" t="n">
         <v>21450</v>
@@ -1590,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>8850</v>
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
         <v>960</v>
@@ -2446,7 +2446,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>12.18</v>
       </c>
       <c r="L5" t="n">
         <v>7623</v>
@@ -2484,7 +2484,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="L6" t="n">
         <v>7936.5</v>
@@ -2522,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="L7" t="n">
         <v>5310</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
         <v>777.6</v>
@@ -3378,7 +3378,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>259848.12</v>
       </c>
       <c r="L5" t="n">
         <v>71808.66</v>
@@ -3416,7 +3416,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>166405.2</v>
       </c>
       <c r="L6" t="n">
         <v>74761.83</v>
@@ -3454,7 +3454,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>52481.64</v>
       </c>
       <c r="L7" t="n">
         <v>50020.2</v>
@@ -3530,7 +3530,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>64002</v>
       </c>
       <c r="L9" t="n">
         <v>7324.99</v>
@@ -4272,7 +4272,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
         <v>33300</v>
@@ -4310,7 +4310,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
         <v>4170</v>
@@ -5242,7 +5242,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="L5" t="n">
         <v>875.7</v>
@@ -6174,7 +6174,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>35841.12</v>
       </c>
       <c r="L5" t="n">
         <v>8249.09</v>
@@ -7068,7 +7068,7 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L4" t="n">
         <v>10860</v>
@@ -7106,7 +7106,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
         <v>1500</v>
@@ -7144,7 +7144,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -8038,7 +8038,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="L5" t="n">
         <v>315</v>
@@ -8076,7 +8076,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -8970,7 +8970,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>44801.4</v>
       </c>
       <c r="L5" t="n">
         <v>2967.3</v>
@@ -9008,7 +9008,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>13867.1</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -9864,7 +9864,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="L4" t="n">
         <v>164250</v>
@@ -9902,7 +9902,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L5" t="n">
         <v>54630</v>
@@ -9940,7 +9940,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
         <v>15180</v>
@@ -10834,7 +10834,7 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>57.96</v>
       </c>
       <c r="L5" t="n">
         <v>48245.4</v>
@@ -10872,7 +10872,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>18.85</v>
       </c>
       <c r="L6" t="n">
         <v>29803.5</v>
@@ -10910,7 +10910,7 @@
         <v>1.4</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>6.56</v>
       </c>
       <c r="L7" t="n">
         <v>25560</v>
@@ -10948,7 +10948,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="L8" t="n">
         <v>12141</v>
@@ -10986,7 +10986,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L9" t="n">
         <v>4787.1</v>
@@ -11766,7 +11766,7 @@
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>7.56</v>
       </c>
       <c r="L5" t="n">
         <v>11472.3</v>
@@ -11804,7 +11804,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="L6" t="n">
         <v>5616.6</v>
@@ -12698,7 +12698,7 @@
         <v>17499.9</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>161285.04</v>
       </c>
       <c r="L5" t="n">
         <v>108069.07</v>
@@ -12736,7 +12736,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>55468.4</v>
       </c>
       <c r="L6" t="n">
         <v>52908.37</v>
@@ -13592,7 +13592,7 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L4" t="n">
         <v>89100</v>
@@ -16426,7 +16426,7 @@
         <v>34999.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1236518.64</v>
       </c>
       <c r="L5" t="n">
         <v>454471.67</v>
@@ -16464,7 +16464,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>402145.9</v>
       </c>
       <c r="L6" t="n">
         <v>280748.97</v>
@@ -16502,7 +16502,7 @@
         <v>81666.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>139951.04</v>
       </c>
       <c r="L7" t="n">
         <v>240775.2</v>
@@ -16540,7 +16540,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>57601.8</v>
       </c>
       <c r="L8" t="n">
         <v>114368.22</v>
@@ -16578,7 +16578,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>128004</v>
       </c>
       <c r="L9" t="n">
         <v>45094.48</v>
@@ -17320,7 +17320,7 @@
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="L4" t="n">
         <v>154290</v>
@@ -17358,7 +17358,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="L5" t="n">
         <v>50040</v>
@@ -17396,7 +17396,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L6" t="n">
         <v>19770</v>
@@ -17434,7 +17434,7 @@
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L7" t="n">
         <v>8160</v>
@@ -17472,7 +17472,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
         <v>2250</v>
@@ -17510,7 +17510,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>810</v>
@@ -18290,7 +18290,7 @@
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>22.26</v>
       </c>
       <c r="L5" t="n">
         <v>10508.4</v>
@@ -18328,7 +18328,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="L6" t="n">
         <v>7314.9</v>
@@ -18366,7 +18366,7 @@
         <v>1.4</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="L7" t="n">
         <v>4896</v>
@@ -18404,7 +18404,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="L8" t="n">
         <v>1597.5</v>
@@ -18442,7 +18442,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>656.1</v>
@@ -19222,7 +19222,7 @@
         <v>17499.9</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>474894.84</v>
       </c>
       <c r="L5" t="n">
         <v>98989.13</v>
@@ -19260,7 +19260,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>124803.9</v>
       </c>
       <c r="L6" t="n">
         <v>68906.36</v>
@@ -19298,7 +19298,7 @@
         <v>81666.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>87469.39999999999</v>
       </c>
       <c r="L7" t="n">
         <v>46120.32</v>
@@ -19336,7 +19336,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>38401.2</v>
       </c>
       <c r="L8" t="n">
         <v>15048.45</v>
@@ -19374,7 +19374,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L9" t="n">
         <v>6180.46</v>
@@ -20116,7 +20116,7 @@
         <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="L4" t="n">
         <v>172140</v>
@@ -20154,7 +20154,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="L5" t="n">
         <v>42840</v>
@@ -20192,7 +20192,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
         <v>4590</v>
@@ -21086,7 +21086,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>11.34</v>
       </c>
       <c r="L5" t="n">
         <v>8996.4</v>
@@ -21124,7 +21124,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="L6" t="n">
         <v>1698.3</v>
@@ -22018,7 +22018,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>241927.56</v>
       </c>
       <c r="L5" t="n">
         <v>84746.09</v>
@@ -22056,7 +22056,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>27734.2</v>
       </c>
       <c r="L6" t="n">
         <v>15997.99</v>

--- a/risk/Risk_Analysis_T3_5yrs_Present_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_5yrs_Present_Perfect.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,13 +511,18 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>90272.25</v>
+        <v>90194.13</v>
       </c>
       <c r="C4" t="n">
         <v>13578264</v>
@@ -532,7 +537,7 @@
         <v>57</v>
       </c>
       <c r="G4" t="n">
-        <v>272340</v>
+        <v>270660</v>
       </c>
       <c r="H4" t="n">
         <v>40230</v>
@@ -544,10 +549,13 @@
         <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="L4" t="n">
-        <v>720180</v>
+        <v>716010</v>
+      </c>
+      <c r="M4" t="n">
+        <v>38100</v>
       </c>
     </row>
     <row r="5">
@@ -555,7 +563,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>32458.5</v>
+        <v>32435.82</v>
       </c>
       <c r="C5" t="n">
         <v>3645432</v>
@@ -570,7 +578,7 @@
         <v>18</v>
       </c>
       <c r="G5" t="n">
-        <v>95880</v>
+        <v>95550</v>
       </c>
       <c r="H5" t="n">
         <v>6180</v>
@@ -582,10 +590,13 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="L5" t="n">
-        <v>229740</v>
+        <v>229410</v>
+      </c>
+      <c r="M5" t="n">
+        <v>18060</v>
       </c>
     </row>
     <row r="6">
@@ -593,7 +604,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>18078.48</v>
+        <v>18077.58</v>
       </c>
       <c r="C6" t="n">
         <v>1249920</v>
@@ -608,7 +619,7 @@
         <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>32010</v>
+        <v>31650</v>
       </c>
       <c r="H6" t="n">
         <v>3810</v>
@@ -620,10 +631,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L6" t="n">
-        <v>80550</v>
+        <v>80370</v>
+      </c>
+      <c r="M6" t="n">
+        <v>6870</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +645,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>11726.64</v>
+        <v>11726.55</v>
       </c>
       <c r="C7" t="n">
         <v>539784</v>
@@ -646,7 +660,7 @@
         <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>16860</v>
+        <v>16560</v>
       </c>
       <c r="H7" t="n">
         <v>240</v>
@@ -661,7 +675,10 @@
         <v>8</v>
       </c>
       <c r="L7" t="n">
-        <v>42600</v>
+        <v>42330</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3900</v>
       </c>
     </row>
     <row r="8">
@@ -684,7 +701,7 @@
         <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>12630</v>
+        <v>12540</v>
       </c>
       <c r="H8" t="n">
         <v>120</v>
@@ -700,6 +717,9 @@
       </c>
       <c r="L8" t="n">
         <v>17100</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1230</v>
       </c>
     </row>
     <row r="9">
@@ -722,7 +742,7 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>2670</v>
+        <v>2490</v>
       </c>
       <c r="H9" t="n">
         <v>90</v>
@@ -738,6 +758,9 @@
       </c>
       <c r="L9" t="n">
         <v>5910</v>
+      </c>
+      <c r="M9" t="n">
+        <v>390</v>
       </c>
     </row>
     <row r="10">
@@ -777,6 +800,9 @@
       <c r="L10" t="n">
         <v>2880</v>
       </c>
+      <c r="M10" t="n">
+        <v>240</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -815,6 +841,9 @@
       <c r="L11" t="n">
         <v>1650</v>
       </c>
+      <c r="M11" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -853,6 +882,9 @@
       <c r="L12" t="n">
         <v>330</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -891,6 +923,9 @@
       <c r="L13" t="n">
         <v>270</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -929,6 +964,9 @@
       <c r="L14" t="n">
         <v>540</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -967,6 +1005,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1005,6 +1046,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1043,6 +1087,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1081,6 +1128,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1119,6 +1169,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1157,6 +1210,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1195,6 +1251,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1233,6 +1292,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1271,6 +1333,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1309,6 +1374,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -1358,6 +1426,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -1372,7 +1444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1443,6 +1515,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1464,7 +1541,7 @@
         <v>8</v>
       </c>
       <c r="G4" t="n">
-        <v>25350</v>
+        <v>25410</v>
       </c>
       <c r="H4" t="n">
         <v>2430</v>
@@ -1479,7 +1556,10 @@
         <v>38</v>
       </c>
       <c r="L4" t="n">
-        <v>59670</v>
+        <v>59760</v>
+      </c>
+      <c r="M4" t="n">
+        <v>7290</v>
       </c>
     </row>
     <row r="5">
@@ -1487,7 +1567,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3957.3</v>
+        <v>3957.21</v>
       </c>
       <c r="C5" t="n">
         <v>430920</v>
@@ -1502,7 +1582,7 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>14250</v>
+        <v>14280</v>
       </c>
       <c r="H5" t="n">
         <v>1950</v>
@@ -1517,7 +1597,10 @@
         <v>29</v>
       </c>
       <c r="L5" t="n">
-        <v>36300</v>
+        <v>36390</v>
+      </c>
+      <c r="M5" t="n">
+        <v>8490</v>
       </c>
     </row>
     <row r="6">
@@ -1557,6 +1640,9 @@
       <c r="L6" t="n">
         <v>21450</v>
       </c>
+      <c r="M6" t="n">
+        <v>3180</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1595,6 +1681,9 @@
       <c r="L7" t="n">
         <v>8850</v>
       </c>
+      <c r="M7" t="n">
+        <v>1980</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1633,6 +1722,9 @@
       <c r="L8" t="n">
         <v>2910</v>
       </c>
+      <c r="M8" t="n">
+        <v>600</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1671,6 +1763,9 @@
       <c r="L9" t="n">
         <v>960</v>
       </c>
+      <c r="M9" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1709,6 +1804,9 @@
       <c r="L10" t="n">
         <v>660</v>
       </c>
+      <c r="M10" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1745,7 +1843,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1140</v>
+        <v>1170</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1785,6 +1886,9 @@
       <c r="L12" t="n">
         <v>240</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1823,6 +1927,9 @@
       <c r="L13" t="n">
         <v>90</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1861,6 +1968,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1899,6 +2009,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1937,6 +2050,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1975,6 +2091,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2013,6 +2132,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2051,6 +2173,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2089,6 +2214,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2127,6 +2255,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2165,6 +2296,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2203,6 +2337,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2241,6 +2378,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -2290,6 +2430,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -2304,7 +2448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2375,6 +2519,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2411,6 +2560,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2419,7 +2571,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>1780.78</v>
+        <v>1780.74</v>
       </c>
       <c r="C5" t="n">
         <v>237006</v>
@@ -2440,16 +2592,19 @@
         <v>702</v>
       </c>
       <c r="I5" t="n">
-        <v>0.15</v>
+        <v>0.33</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>12.18</v>
+        <v>9.6</v>
       </c>
       <c r="L5" t="n">
-        <v>7623</v>
+        <v>7641.9</v>
+      </c>
+      <c r="M5" t="n">
+        <v>169.8</v>
       </c>
     </row>
     <row r="6">
@@ -2484,10 +2639,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>7.8</v>
+        <v>6.08</v>
       </c>
       <c r="L6" t="n">
         <v>7936.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>254.4</v>
       </c>
     </row>
     <row r="7">
@@ -2522,10 +2680,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2.46</v>
+        <v>1.91</v>
       </c>
       <c r="L7" t="n">
         <v>5310</v>
+      </c>
+      <c r="M7" t="n">
+        <v>693</v>
       </c>
     </row>
     <row r="8">
@@ -2565,6 +2726,9 @@
       <c r="L8" t="n">
         <v>2066.1</v>
       </c>
+      <c r="M8" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -2598,10 +2762,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>2.41</v>
       </c>
       <c r="L9" t="n">
         <v>777.6</v>
+      </c>
+      <c r="M9" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="10">
@@ -2641,6 +2808,9 @@
       <c r="L10" t="n">
         <v>587.4</v>
       </c>
+      <c r="M10" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2677,7 +2847,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1140</v>
+        <v>1170</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -2717,6 +2890,9 @@
       <c r="L12" t="n">
         <v>240</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2755,6 +2931,9 @@
       <c r="L13" t="n">
         <v>90</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2793,6 +2972,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2831,6 +3013,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2869,6 +3054,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2907,6 +3095,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2945,6 +3136,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2983,6 +3177,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3021,6 +3218,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3059,6 +3259,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3097,6 +3300,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3135,6 +3341,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3173,6 +3382,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -3222,6 +3434,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -3236,7 +3452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3307,6 +3523,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -3343,6 +3564,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3351,16 +3575,16 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3917727</v>
+        <v>3917637.9</v>
       </c>
       <c r="C5" t="n">
-        <v>13035330</v>
+        <v>9954252</v>
       </c>
       <c r="D5" t="n">
-        <v>11356051.07</v>
+        <v>21517436.16</v>
       </c>
       <c r="E5" t="n">
-        <v>2085003.55</v>
+        <v>3904289.1</v>
       </c>
       <c r="F5" t="n">
         <v>2500.02</v>
@@ -3369,19 +3593,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>194208.3</v>
+        <v>4001400</v>
       </c>
       <c r="I5" t="n">
-        <v>57499.5</v>
+        <v>64288.14</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>259848.12</v>
+        <v>466089.04</v>
       </c>
       <c r="L5" t="n">
-        <v>71808.66</v>
+        <v>1375542</v>
+      </c>
+      <c r="M5" t="n">
+        <v>50940</v>
       </c>
     </row>
     <row r="6">
@@ -3392,22 +3619,22 @@
         <v>7111526.4</v>
       </c>
       <c r="C6" t="n">
-        <v>12474000</v>
+        <v>9525600</v>
       </c>
       <c r="D6" t="n">
-        <v>10172113.38</v>
+        <v>19274112</v>
       </c>
       <c r="E6" t="n">
-        <v>1849511.66</v>
+        <v>3463317</v>
       </c>
       <c r="F6" t="n">
         <v>8333.4</v>
       </c>
       <c r="G6" t="n">
-        <v>6493.5</v>
+        <v>18954</v>
       </c>
       <c r="H6" t="n">
-        <v>525109.36</v>
+        <v>10819170</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -3416,10 +3643,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>166405.2</v>
+        <v>295414.7</v>
       </c>
       <c r="L6" t="n">
-        <v>74761.83</v>
+        <v>1428570</v>
+      </c>
+      <c r="M6" t="n">
+        <v>76320</v>
       </c>
     </row>
     <row r="7">
@@ -3430,22 +3660,22 @@
         <v>7437097.8</v>
       </c>
       <c r="C7" t="n">
-        <v>6597360</v>
+        <v>5037984</v>
       </c>
       <c r="D7" t="n">
-        <v>6092995.6</v>
+        <v>11545003.01</v>
       </c>
       <c r="E7" t="n">
-        <v>1022802.83</v>
+        <v>1915257.15</v>
       </c>
       <c r="F7" t="n">
         <v>25000.2</v>
       </c>
       <c r="G7" t="n">
-        <v>10073.25</v>
+        <v>29403</v>
       </c>
       <c r="H7" t="n">
-        <v>18175.9</v>
+        <v>374490</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3454,10 +3684,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>52481.64</v>
+        <v>92936.17999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>50020.2</v>
+        <v>955800</v>
+      </c>
+      <c r="M7" t="n">
+        <v>207900</v>
       </c>
     </row>
     <row r="8">
@@ -3468,22 +3701,22 @@
         <v>4961880</v>
       </c>
       <c r="C8" t="n">
-        <v>2688840</v>
+        <v>2053296</v>
       </c>
       <c r="D8" t="n">
-        <v>2864723.94</v>
+        <v>5428076.54</v>
       </c>
       <c r="E8" t="n">
-        <v>284722.65</v>
+        <v>533159.55</v>
       </c>
       <c r="F8" t="n">
         <v>79167.3</v>
       </c>
       <c r="G8" t="n">
-        <v>56998.5</v>
+        <v>166374</v>
       </c>
       <c r="H8" t="n">
-        <v>14109.15</v>
+        <v>290700</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -3495,7 +3728,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>19462.66</v>
+        <v>371898</v>
+      </c>
+      <c r="M8" t="n">
+        <v>108000</v>
       </c>
     </row>
     <row r="9">
@@ -3506,22 +3742,22 @@
         <v>2136420</v>
       </c>
       <c r="C9" t="n">
-        <v>720720</v>
+        <v>550368</v>
       </c>
       <c r="D9" t="n">
-        <v>837764.83</v>
+        <v>1587396.1</v>
       </c>
       <c r="E9" t="n">
-        <v>44388.94</v>
+        <v>83120.85000000001</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>13680.75</v>
+        <v>39933</v>
       </c>
       <c r="H9" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -3530,10 +3766,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>64002</v>
+        <v>116971.4</v>
       </c>
       <c r="L9" t="n">
-        <v>7324.99</v>
+        <v>139968</v>
+      </c>
+      <c r="M9" t="n">
+        <v>45000</v>
       </c>
     </row>
     <row r="10">
@@ -3544,22 +3783,22 @@
         <v>962874</v>
       </c>
       <c r="C10" t="n">
-        <v>443520</v>
+        <v>338688</v>
       </c>
       <c r="D10" t="n">
-        <v>558563.39</v>
+        <v>1058365.44</v>
       </c>
       <c r="E10" t="n">
-        <v>48086.64</v>
+        <v>90045</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2220</v>
+        <v>6480</v>
       </c>
       <c r="H10" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -3571,7 +3810,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>5533.31</v>
+        <v>105732</v>
+      </c>
+      <c r="M10" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="11">
@@ -3582,10 +3824,10 @@
         <v>647460</v>
       </c>
       <c r="C11" t="n">
-        <v>471240</v>
+        <v>359856</v>
       </c>
       <c r="D11" t="n">
-        <v>612914.97</v>
+        <v>1161350.78</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -3594,7 +3836,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>3885</v>
+        <v>11340</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -3609,7 +3851,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>10738.8</v>
+        <v>210600</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -3620,10 +3865,10 @@
         <v>533214</v>
       </c>
       <c r="C12" t="n">
-        <v>221760</v>
+        <v>169344</v>
       </c>
       <c r="D12" t="n">
-        <v>297579.46</v>
+        <v>563853.3100000001</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -3632,10 +3877,10 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2220</v>
+        <v>6480</v>
       </c>
       <c r="H12" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -3647,7 +3892,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2260.8</v>
+        <v>43200</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3658,10 +3906,10 @@
         <v>626868</v>
       </c>
       <c r="C13" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D13" t="n">
-        <v>152401.13</v>
+        <v>288769.54</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -3673,7 +3921,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -3685,7 +3933,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>847.8</v>
+        <v>16200</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -3696,10 +3947,10 @@
         <v>703494</v>
       </c>
       <c r="C14" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D14" t="n">
-        <v>156012.53</v>
+        <v>295612.42</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -3723,6 +3974,9 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3734,10 +3988,10 @@
         <v>278586</v>
       </c>
       <c r="C15" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D15" t="n">
-        <v>79129.81</v>
+        <v>149935.1</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -3761,6 +4015,9 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3772,10 +4029,10 @@
         <v>211662</v>
       </c>
       <c r="C16" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D16" t="n">
-        <v>160506.72</v>
+        <v>304128</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -3799,6 +4056,9 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3839,6 +4099,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3877,6 +4140,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3915,6 +4181,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3953,6 +4222,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3991,6 +4263,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4029,6 +4304,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4067,6 +4345,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -4105,6 +4386,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -4154,6 +4438,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -4168,7 +4456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4239,6 +4527,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -4275,7 +4568,10 @@
         <v>7</v>
       </c>
       <c r="L4" t="n">
-        <v>33300</v>
+        <v>33450</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -4315,6 +4611,9 @@
       <c r="L5" t="n">
         <v>4170</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -4353,6 +4652,9 @@
       <c r="L6" t="n">
         <v>420</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -4391,6 +4693,9 @@
       <c r="L7" t="n">
         <v>90</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -4429,6 +4734,9 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -4467,6 +4775,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -4505,6 +4816,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -4543,6 +4857,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -4581,6 +4898,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -4619,6 +4939,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -4657,6 +4980,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -4695,6 +5021,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -4733,6 +5062,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -4771,6 +5103,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -4809,6 +5144,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -4847,6 +5185,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -4885,6 +5226,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -4923,6 +5267,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4961,6 +5308,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4999,6 +5349,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -5037,6 +5390,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -5086,6 +5442,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -5100,7 +5460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5171,6 +5531,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -5207,6 +5572,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5242,10 +5610,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1.68</v>
+        <v>1.32</v>
       </c>
       <c r="L5" t="n">
         <v>875.7</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -5285,6 +5656,9 @@
       <c r="L6" t="n">
         <v>155.4</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -5323,6 +5697,9 @@
       <c r="L7" t="n">
         <v>54</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -5361,6 +5738,9 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -5399,6 +5779,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -5437,6 +5820,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -5475,6 +5861,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -5513,6 +5902,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -5551,6 +5943,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -5589,6 +5984,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -5627,6 +6025,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -5665,6 +6066,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -5703,6 +6107,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -5741,6 +6148,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -5779,6 +6189,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -5817,6 +6230,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -5855,6 +6271,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -5893,6 +6312,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -5931,6 +6353,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -5969,6 +6394,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -6018,6 +6446,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -6032,7 +6464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6103,6 +6535,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -6139,6 +6576,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6150,13 +6590,13 @@
         <v>194505.3</v>
       </c>
       <c r="C5" t="n">
-        <v>1509354</v>
+        <v>1152597.6</v>
       </c>
       <c r="D5" t="n">
-        <v>1314911.18</v>
+        <v>2491492.61</v>
       </c>
       <c r="E5" t="n">
-        <v>219474.06</v>
+        <v>410977.8</v>
       </c>
       <c r="F5" t="n">
         <v>833.34</v>
@@ -6174,10 +6614,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>35841.12</v>
+        <v>64288.14</v>
       </c>
       <c r="L5" t="n">
-        <v>8249.09</v>
+        <v>157626</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -6188,10 +6631,10 @@
         <v>25819.2</v>
       </c>
       <c r="C6" t="n">
-        <v>99792</v>
+        <v>76204.8</v>
       </c>
       <c r="D6" t="n">
-        <v>81376.91</v>
+        <v>154192.9</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -6200,7 +6643,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>194.25</v>
+        <v>567</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -6215,7 +6658,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1463.87</v>
+        <v>27972</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -6253,7 +6699,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>508.68</v>
+        <v>9720</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -6276,7 +6725,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>360.75</v>
+        <v>1053</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -6291,6 +6740,9 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6331,6 +6783,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -6369,6 +6824,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -6407,6 +6865,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -6445,6 +6906,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -6483,6 +6947,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -6521,6 +6988,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -6559,6 +7029,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -6597,6 +7070,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -6635,6 +7111,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -6673,6 +7152,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -6711,6 +7193,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -6749,6 +7234,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -6787,6 +7275,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -6825,6 +7316,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -6863,6 +7357,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -6901,6 +7398,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -6950,6 +7450,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -6964,7 +7468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7035,6 +7539,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -7072,6 +7581,9 @@
       </c>
       <c r="L4" t="n">
         <v>10860</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -7111,6 +7623,9 @@
       <c r="L5" t="n">
         <v>1500</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -7149,6 +7664,9 @@
       <c r="L6" t="n">
         <v>0</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -7187,6 +7705,9 @@
       <c r="L7" t="n">
         <v>0</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -7225,6 +7746,9 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -7263,6 +7787,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -7301,6 +7828,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -7339,6 +7869,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -7377,6 +7910,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -7415,6 +7951,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -7453,6 +7992,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -7491,6 +8033,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -7529,6 +8074,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -7567,6 +8115,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -7605,6 +8156,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -7643,6 +8197,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -7681,6 +8238,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -7719,6 +8279,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -7757,6 +8320,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -7795,6 +8361,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -7833,6 +8402,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -7882,6 +8454,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -7896,7 +8472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7967,6 +8543,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -8003,6 +8584,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8038,10 +8622,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="L5" t="n">
         <v>315</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -8076,9 +8663,12 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.65</v>
+        <v>0.51</v>
       </c>
       <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8119,6 +8709,9 @@
       <c r="L7" t="n">
         <v>0</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -8157,6 +8750,9 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -8195,6 +8791,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -8233,6 +8832,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -8271,6 +8873,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -8309,6 +8914,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -8347,6 +8955,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -8385,6 +8996,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -8423,6 +9037,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -8461,6 +9078,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -8499,6 +9119,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -8537,6 +9160,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -8575,6 +9201,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -8613,6 +9242,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -8651,6 +9283,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -8689,6 +9324,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -8727,6 +9365,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -8765,6 +9406,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -8814,6 +9458,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -8828,7 +9476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8899,6 +9547,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -8935,6 +9588,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8946,13 +9602,13 @@
         <v>608998.5</v>
       </c>
       <c r="C5" t="n">
-        <v>1646568</v>
+        <v>1257379.2</v>
       </c>
       <c r="D5" t="n">
-        <v>1434448.56</v>
+        <v>2717991.94</v>
       </c>
       <c r="E5" t="n">
-        <v>54868.51</v>
+        <v>102744.45</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -8961,7 +9617,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>32866.02</v>
+        <v>677160</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -8970,10 +9626,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>44801.4</v>
+        <v>80360.17999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>2967.3</v>
+        <v>56700</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -8984,10 +9643,10 @@
         <v>176774.4</v>
       </c>
       <c r="C6" t="n">
-        <v>573804</v>
+        <v>438177.6</v>
       </c>
       <c r="D6" t="n">
-        <v>467917.22</v>
+        <v>886609.15</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -8996,7 +9655,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>582.75</v>
+        <v>1701</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -9008,9 +9667,12 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>13867.1</v>
+        <v>24617.89</v>
       </c>
       <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9051,6 +9713,9 @@
       <c r="L7" t="n">
         <v>0</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -9060,10 +9725,10 @@
         <v>6138</v>
       </c>
       <c r="C8" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D8" t="n">
-        <v>29533.24</v>
+        <v>55959.55</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -9087,6 +9752,9 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9127,6 +9795,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -9165,6 +9836,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -9203,6 +9877,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -9241,6 +9918,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -9279,6 +9959,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -9317,6 +10000,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -9355,6 +10041,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -9393,6 +10082,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -9431,6 +10123,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -9469,6 +10164,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -9507,6 +10205,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -9545,6 +10246,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -9583,6 +10287,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -9621,6 +10328,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -9659,6 +10369,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -9697,6 +10410,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -9746,6 +10462,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -9760,7 +10480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9831,6 +10551,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -9852,7 +10577,7 @@
         <v>11</v>
       </c>
       <c r="G4" t="n">
-        <v>60330</v>
+        <v>60390</v>
       </c>
       <c r="H4" t="n">
         <v>10200</v>
@@ -9864,10 +10589,13 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L4" t="n">
-        <v>164250</v>
+        <v>164370</v>
+      </c>
+      <c r="M4" t="n">
+        <v>10080</v>
       </c>
     </row>
     <row r="5">
@@ -9890,7 +10618,7 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>14100</v>
+        <v>14130</v>
       </c>
       <c r="H5" t="n">
         <v>1170</v>
@@ -9905,7 +10633,10 @@
         <v>18</v>
       </c>
       <c r="L5" t="n">
-        <v>54630</v>
+        <v>54660</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3810</v>
       </c>
     </row>
     <row r="6">
@@ -9945,6 +10676,9 @@
       <c r="L6" t="n">
         <v>15180</v>
       </c>
+      <c r="M6" t="n">
+        <v>1800</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -9983,6 +10717,9 @@
       <c r="L7" t="n">
         <v>6840</v>
       </c>
+      <c r="M7" t="n">
+        <v>480</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -10021,6 +10758,9 @@
       <c r="L8" t="n">
         <v>3120</v>
       </c>
+      <c r="M8" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -10059,6 +10799,9 @@
       <c r="L9" t="n">
         <v>2310</v>
       </c>
+      <c r="M9" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -10097,6 +10840,9 @@
       <c r="L10" t="n">
         <v>960</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -10135,6 +10881,9 @@
       <c r="L11" t="n">
         <v>180</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -10173,6 +10922,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -10211,6 +10963,9 @@
       <c r="L13" t="n">
         <v>30</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -10249,6 +11004,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -10287,6 +11045,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -10325,6 +11086,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -10363,6 +11127,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -10401,6 +11168,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -10439,6 +11209,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -10477,6 +11250,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -10515,6 +11291,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -10553,6 +11332,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -10591,6 +11373,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -10629,6 +11414,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -10678,6 +11466,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -10692,7 +11484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10763,6 +11555,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -10799,6 +11596,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10807,7 +11607,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>14606.32</v>
+        <v>14596.12</v>
       </c>
       <c r="C5" t="n">
         <v>2004987.6</v>
@@ -10828,16 +11628,19 @@
         <v>2224.8</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3</v>
+        <v>0.66</v>
       </c>
       <c r="J5" t="n">
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>57.96</v>
+        <v>43.03</v>
       </c>
       <c r="L5" t="n">
-        <v>48245.4</v>
+        <v>48176.1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>361.2</v>
       </c>
     </row>
     <row r="6">
@@ -10845,7 +11648,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>14462.78</v>
+        <v>14462.06</v>
       </c>
       <c r="C6" t="n">
         <v>1124928</v>
@@ -10860,7 +11663,7 @@
         <v>0.6</v>
       </c>
       <c r="G6" t="n">
-        <v>1600.5</v>
+        <v>1582.5</v>
       </c>
       <c r="H6" t="n">
         <v>2171.7</v>
@@ -10872,10 +11675,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>18.85</v>
+        <v>14.2</v>
       </c>
       <c r="L6" t="n">
-        <v>29803.5</v>
+        <v>29736.9</v>
+      </c>
+      <c r="M6" t="n">
+        <v>549.6</v>
       </c>
     </row>
     <row r="7">
@@ -10883,7 +11689,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>11140.31</v>
+        <v>11140.22</v>
       </c>
       <c r="C7" t="n">
         <v>539784</v>
@@ -10898,7 +11704,7 @@
         <v>2.4</v>
       </c>
       <c r="G7" t="n">
-        <v>2529</v>
+        <v>2484</v>
       </c>
       <c r="H7" t="n">
         <v>175.2</v>
@@ -10910,10 +11716,13 @@
         <v>1.4</v>
       </c>
       <c r="K7" t="n">
-        <v>6.56</v>
+        <v>5.1</v>
       </c>
       <c r="L7" t="n">
-        <v>25560</v>
+        <v>25398</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1365</v>
       </c>
     </row>
     <row r="8">
@@ -10936,7 +11745,7 @@
         <v>2.85</v>
       </c>
       <c r="G8" t="n">
-        <v>8209.5</v>
+        <v>8151</v>
       </c>
       <c r="H8" t="n">
         <v>102</v>
@@ -10948,10 +11757,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2.7</v>
+        <v>2.21</v>
       </c>
       <c r="L8" t="n">
         <v>12141</v>
+      </c>
+      <c r="M8" t="n">
+        <v>738</v>
       </c>
     </row>
     <row r="9">
@@ -10974,7 +11786,7 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>2269.5</v>
+        <v>2116.5</v>
       </c>
       <c r="H9" t="n">
         <v>90</v>
@@ -10986,10 +11798,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>4.82</v>
       </c>
       <c r="L9" t="n">
         <v>4787.1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>390</v>
       </c>
     </row>
     <row r="10">
@@ -11029,6 +11844,9 @@
       <c r="L10" t="n">
         <v>2563.2</v>
       </c>
+      <c r="M10" t="n">
+        <v>240</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -11067,6 +11885,9 @@
       <c r="L11" t="n">
         <v>1650</v>
       </c>
+      <c r="M11" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -11105,6 +11926,9 @@
       <c r="L12" t="n">
         <v>330</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -11143,6 +11967,9 @@
       <c r="L13" t="n">
         <v>270</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -11181,6 +12008,9 @@
       <c r="L14" t="n">
         <v>540</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -11219,6 +12049,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -11257,6 +12090,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -11295,6 +12131,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -11333,6 +12172,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -11371,6 +12213,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -11409,6 +12254,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -11447,6 +12295,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -11485,6 +12336,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -11523,6 +12377,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -11561,6 +12418,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -11610,6 +12470,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -11624,7 +12488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11695,6 +12559,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -11731,6 +12600,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11760,16 +12632,19 @@
         <v>421.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.15</v>
+        <v>0.33</v>
       </c>
       <c r="J5" t="n">
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>7.56</v>
+        <v>5.96</v>
       </c>
       <c r="L5" t="n">
-        <v>11472.3</v>
+        <v>11478.6</v>
+      </c>
+      <c r="M5" t="n">
+        <v>76.2</v>
       </c>
     </row>
     <row r="6">
@@ -11804,10 +12679,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>2.6</v>
+        <v>2.03</v>
       </c>
       <c r="L6" t="n">
         <v>5616.6</v>
+      </c>
+      <c r="M6" t="n">
+        <v>144</v>
       </c>
     </row>
     <row r="7">
@@ -11847,6 +12725,9 @@
       <c r="L7" t="n">
         <v>4104</v>
       </c>
+      <c r="M7" t="n">
+        <v>168</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -11885,6 +12766,9 @@
       <c r="L8" t="n">
         <v>2215.2</v>
       </c>
+      <c r="M8" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -11923,6 +12807,9 @@
       <c r="L9" t="n">
         <v>1871.1</v>
       </c>
+      <c r="M9" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -11961,6 +12848,9 @@
       <c r="L10" t="n">
         <v>854.4</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -11999,6 +12889,9 @@
       <c r="L11" t="n">
         <v>180</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -12037,6 +12930,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -12075,6 +12971,9 @@
       <c r="L13" t="n">
         <v>30</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -12113,6 +13012,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -12151,6 +13053,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -12189,6 +13094,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -12227,6 +13135,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -12265,6 +13176,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -12303,6 +13217,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -12341,6 +13258,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -12379,6 +13299,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -12417,6 +13340,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -12455,6 +13381,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -12493,6 +13422,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -12542,6 +13474,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -12556,7 +13492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12627,6 +13563,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -12663,6 +13604,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12674,13 +13618,13 @@
         <v>4828774.5</v>
       </c>
       <c r="C5" t="n">
-        <v>12455982</v>
+        <v>9511840.800000001</v>
       </c>
       <c r="D5" t="n">
-        <v>10851337.69</v>
+        <v>20561105.66</v>
       </c>
       <c r="E5" t="n">
-        <v>768159.2</v>
+        <v>1438422.3</v>
       </c>
       <c r="F5" t="n">
         <v>2500.02</v>
@@ -12689,19 +13633,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>116524.98</v>
+        <v>2400840</v>
       </c>
       <c r="I5" t="n">
-        <v>57499.5</v>
+        <v>64288.14</v>
       </c>
       <c r="J5" t="n">
-        <v>17499.9</v>
+        <v>7283.4</v>
       </c>
       <c r="K5" t="n">
-        <v>161285.04</v>
+        <v>289296.65</v>
       </c>
       <c r="L5" t="n">
-        <v>108069.07</v>
+        <v>2066148</v>
+      </c>
+      <c r="M5" t="n">
+        <v>22860</v>
       </c>
     </row>
     <row r="6">
@@ -12712,22 +13659,22 @@
         <v>2535192</v>
       </c>
       <c r="C6" t="n">
-        <v>3293136</v>
+        <v>2514758.4</v>
       </c>
       <c r="D6" t="n">
-        <v>2685437.93</v>
+        <v>5088365.57</v>
       </c>
       <c r="E6" t="n">
-        <v>56045.81</v>
+        <v>104949</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1332</v>
+        <v>3888</v>
       </c>
       <c r="H6" t="n">
-        <v>9461.43</v>
+        <v>194940</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -12736,10 +13683,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>55468.4</v>
+        <v>98471.57000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>52908.37</v>
+        <v>1010988</v>
+      </c>
+      <c r="M6" t="n">
+        <v>43200</v>
       </c>
     </row>
     <row r="7">
@@ -12750,10 +13700,10 @@
         <v>426798.9</v>
       </c>
       <c r="C7" t="n">
-        <v>360360</v>
+        <v>275184</v>
       </c>
       <c r="D7" t="n">
-        <v>332810.68</v>
+        <v>630609.41</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -12762,7 +13712,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1665</v>
+        <v>4860</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -12777,7 +13727,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>38659.68</v>
+        <v>738720</v>
+      </c>
+      <c r="M7" t="n">
+        <v>50400</v>
       </c>
     </row>
     <row r="8">
@@ -12788,10 +13741,10 @@
         <v>208296</v>
       </c>
       <c r="C8" t="n">
-        <v>332640</v>
+        <v>254016</v>
       </c>
       <c r="D8" t="n">
-        <v>354398.84</v>
+        <v>671514.62</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -12800,7 +13753,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>45815.25</v>
+        <v>133731</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -12815,7 +13768,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>20867.18</v>
+        <v>398736</v>
+      </c>
+      <c r="M8" t="n">
+        <v>32400</v>
       </c>
     </row>
     <row r="9">
@@ -12826,10 +13782,10 @@
         <v>145926</v>
       </c>
       <c r="C9" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D9" t="n">
-        <v>32221.72</v>
+        <v>61053.7</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -12838,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2358.75</v>
+        <v>6885</v>
       </c>
       <c r="H9" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -12853,7 +13809,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>17625.76</v>
+        <v>336798</v>
+      </c>
+      <c r="M9" t="n">
+        <v>27000</v>
       </c>
     </row>
     <row r="10">
@@ -12876,7 +13835,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>555</v>
+        <v>1620</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -12891,7 +13850,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>8048.45</v>
+        <v>153792</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -12914,7 +13876,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>555</v>
+        <v>1620</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -12929,7 +13891,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1695.6</v>
+        <v>32400</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -12940,10 +13905,10 @@
         <v>7524</v>
       </c>
       <c r="C12" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D12" t="n">
-        <v>37197.43</v>
+        <v>70481.66</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -12967,6 +13932,9 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13005,7 +13973,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>282.6</v>
+        <v>5400</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -13045,6 +14016,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -13054,10 +14028,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D15" t="n">
-        <v>39564.91</v>
+        <v>74967.55</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13081,6 +14055,9 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13121,6 +14098,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -13159,6 +14139,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -13197,6 +14180,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -13235,6 +14221,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -13273,6 +14262,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -13311,6 +14303,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -13349,6 +14344,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -13387,6 +14385,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -13425,6 +14426,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -13474,6 +14478,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -13488,7 +14496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13559,6 +14567,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -13580,7 +14593,7 @@
         <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>19770</v>
+        <v>19830</v>
       </c>
       <c r="H4" t="n">
         <v>2100</v>
@@ -13595,7 +14608,10 @@
         <v>25</v>
       </c>
       <c r="L4" t="n">
-        <v>89100</v>
+        <v>89490</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -13618,7 +14634,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1830</v>
+        <v>1950</v>
       </c>
       <c r="H5" t="n">
         <v>90</v>
@@ -13633,7 +14649,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>13440</v>
+        <v>13710</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -13673,6 +14692,9 @@
       <c r="L6" t="n">
         <v>720</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -13711,6 +14733,9 @@
       <c r="L7" t="n">
         <v>120</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -13749,6 +14774,9 @@
       <c r="L8" t="n">
         <v>150</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -13787,6 +14815,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -13825,6 +14856,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -13863,6 +14897,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -13901,6 +14938,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -13939,6 +14979,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -13977,6 +15020,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -14015,6 +15061,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -14053,6 +15102,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -14091,6 +15143,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -14129,6 +15184,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -14167,6 +15225,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -14205,6 +15266,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -14243,6 +15307,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -14281,6 +15348,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -14319,6 +15389,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -14357,6 +15430,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -14406,6 +15482,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -14420,7 +15500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14491,6 +15571,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -14527,6 +15612,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14565,7 +15653,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>2822.4</v>
+        <v>2879.1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -14605,6 +15696,9 @@
       <c r="L6" t="n">
         <v>266.4</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -14643,6 +15737,9 @@
       <c r="L7" t="n">
         <v>72</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -14681,6 +15778,9 @@
       <c r="L8" t="n">
         <v>106.5</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -14719,6 +15819,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -14757,6 +15860,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -14795,6 +15901,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -14833,6 +15942,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -14871,6 +15983,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -14909,6 +16024,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -14947,6 +16065,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -14985,6 +16106,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -15023,6 +16147,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -15061,6 +16188,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -15099,6 +16229,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -15137,6 +16270,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -15175,6 +16311,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -15213,6 +16352,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -15251,6 +16393,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -15289,6 +16434,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -15338,6 +16486,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -15352,7 +16504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15423,6 +16575,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -15459,6 +16616,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15470,13 +16630,13 @@
         <v>583337.7</v>
       </c>
       <c r="C5" t="n">
-        <v>1875258</v>
+        <v>1432015.2</v>
       </c>
       <c r="D5" t="n">
-        <v>1633677.52</v>
+        <v>3095490.82</v>
       </c>
       <c r="E5" t="n">
-        <v>365790.1</v>
+        <v>684963</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -15485,7 +16645,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>8963.459999999999</v>
+        <v>184680</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -15497,7 +16657,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>26587.01</v>
+        <v>518238</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -15508,19 +16671,19 @@
         <v>117691.2</v>
       </c>
       <c r="C6" t="n">
-        <v>74844</v>
+        <v>57153.6</v>
       </c>
       <c r="D6" t="n">
-        <v>61032.68</v>
+        <v>115644.67</v>
       </c>
       <c r="E6" t="n">
-        <v>28022.9</v>
+        <v>52474.5</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>166.5</v>
+        <v>486</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -15535,7 +16698,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>2509.49</v>
+        <v>47952</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -15558,7 +16724,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>83.25</v>
+        <v>243</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -15573,7 +16739,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>678.24</v>
+        <v>12960</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -15611,7 +16780,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1003.23</v>
+        <v>19170</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -15651,6 +16823,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -15689,6 +16864,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -15727,6 +16905,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -15765,6 +16946,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -15803,6 +16987,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -15841,6 +17028,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -15879,6 +17069,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -15917,6 +17110,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -15955,6 +17151,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -15993,6 +17192,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -16031,6 +17233,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -16069,6 +17274,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -16107,6 +17315,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -16145,6 +17356,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -16183,6 +17397,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -16221,6 +17438,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -16270,6 +17490,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -16284,7 +17508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16355,6 +17579,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -16391,6 +17620,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16399,16 +17631,16 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>32133915</v>
+        <v>32111461.8</v>
       </c>
       <c r="C5" t="n">
-        <v>110274318</v>
+        <v>84209479.2</v>
       </c>
       <c r="D5" t="n">
-        <v>96068207.5</v>
+        <v>182029959.94</v>
       </c>
       <c r="E5" t="n">
-        <v>11339492.98</v>
+        <v>21233853</v>
       </c>
       <c r="F5" t="n">
         <v>15000.12</v>
@@ -16417,19 +17649,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>615490.92</v>
+        <v>12681360</v>
       </c>
       <c r="I5" t="n">
-        <v>114999</v>
+        <v>128576.29</v>
       </c>
       <c r="J5" t="n">
-        <v>34999.8</v>
+        <v>14566.8</v>
       </c>
       <c r="K5" t="n">
-        <v>1236518.64</v>
+        <v>2089364.68</v>
       </c>
       <c r="L5" t="n">
-        <v>454471.67</v>
+        <v>8671698</v>
+      </c>
+      <c r="M5" t="n">
+        <v>108360</v>
       </c>
     </row>
     <row r="6">
@@ -16437,25 +17672,25 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>31818124.8</v>
+        <v>31816540.8</v>
       </c>
       <c r="C6" t="n">
-        <v>61871040</v>
+        <v>47246976</v>
       </c>
       <c r="D6" t="n">
-        <v>50453682.36</v>
+        <v>95599595.52</v>
       </c>
       <c r="E6" t="n">
-        <v>6080970.17</v>
+        <v>11386966.5</v>
       </c>
       <c r="F6" t="n">
         <v>25000.2</v>
       </c>
       <c r="G6" t="n">
-        <v>29609.25</v>
+        <v>85455</v>
       </c>
       <c r="H6" t="n">
-        <v>600800.8</v>
+        <v>12378690</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -16464,10 +17699,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>402145.9</v>
+        <v>689300.98</v>
       </c>
       <c r="L6" t="n">
-        <v>280748.97</v>
+        <v>5352642</v>
+      </c>
+      <c r="M6" t="n">
+        <v>164880</v>
       </c>
     </row>
     <row r="7">
@@ -16475,37 +17713,40 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>24508677.6</v>
+        <v>24508489.5</v>
       </c>
       <c r="C7" t="n">
-        <v>29688120</v>
+        <v>22670928</v>
       </c>
       <c r="D7" t="n">
-        <v>27418480.19</v>
+        <v>51952513.54</v>
       </c>
       <c r="E7" t="n">
-        <v>2962601.31</v>
+        <v>5547641.4</v>
       </c>
       <c r="F7" t="n">
         <v>100000.8</v>
       </c>
       <c r="G7" t="n">
-        <v>46786.5</v>
+        <v>134136</v>
       </c>
       <c r="H7" t="n">
-        <v>48469.08</v>
+        <v>998640</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>81666.2</v>
+        <v>33989.2</v>
       </c>
       <c r="K7" t="n">
-        <v>139951.04</v>
+        <v>247829.82</v>
       </c>
       <c r="L7" t="n">
-        <v>240775.2</v>
+        <v>4571640</v>
+      </c>
+      <c r="M7" t="n">
+        <v>409500</v>
       </c>
     </row>
     <row r="8">
@@ -16516,22 +17757,22 @@
         <v>15489738</v>
       </c>
       <c r="C8" t="n">
-        <v>10395000</v>
+        <v>7938000</v>
       </c>
       <c r="D8" t="n">
-        <v>11074963.68</v>
+        <v>20984832</v>
       </c>
       <c r="E8" t="n">
-        <v>1220239.94</v>
+        <v>2284969.5</v>
       </c>
       <c r="F8" t="n">
         <v>118750.95</v>
       </c>
       <c r="G8" t="n">
-        <v>151875.75</v>
+        <v>440154</v>
       </c>
       <c r="H8" t="n">
-        <v>28218.3</v>
+        <v>581400</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -16540,10 +17781,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>57601.8</v>
+        <v>107211.65</v>
       </c>
       <c r="L8" t="n">
-        <v>114368.22</v>
+        <v>2185380</v>
+      </c>
+      <c r="M8" t="n">
+        <v>221400</v>
       </c>
     </row>
     <row r="9">
@@ -16554,22 +17798,22 @@
         <v>8161758</v>
       </c>
       <c r="C9" t="n">
-        <v>4296600</v>
+        <v>3281040</v>
       </c>
       <c r="D9" t="n">
-        <v>4994367.23</v>
+        <v>9463322.880000001</v>
       </c>
       <c r="E9" t="n">
-        <v>843389.92</v>
+        <v>1579296.15</v>
       </c>
       <c r="F9" t="n">
         <v>41667</v>
       </c>
       <c r="G9" t="n">
-        <v>41985.75</v>
+        <v>114291</v>
       </c>
       <c r="H9" t="n">
-        <v>24898.5</v>
+        <v>513000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -16578,10 +17822,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>128004</v>
+        <v>233942.81</v>
       </c>
       <c r="L9" t="n">
-        <v>45094.48</v>
+        <v>861678</v>
+      </c>
+      <c r="M9" t="n">
+        <v>117000</v>
       </c>
     </row>
     <row r="10">
@@ -16592,22 +17839,22 @@
         <v>4180968</v>
       </c>
       <c r="C10" t="n">
-        <v>1247400</v>
+        <v>952560</v>
       </c>
       <c r="D10" t="n">
-        <v>1570959.52</v>
+        <v>2976652.8</v>
       </c>
       <c r="E10" t="n">
-        <v>48086.64</v>
+        <v>90045</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>14985</v>
+        <v>43740</v>
       </c>
       <c r="H10" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -16619,7 +17866,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>24145.34</v>
+        <v>461376</v>
+      </c>
+      <c r="M10" t="n">
+        <v>72000</v>
       </c>
     </row>
     <row r="11">
@@ -16630,19 +17880,19 @@
         <v>2471040</v>
       </c>
       <c r="C11" t="n">
-        <v>970200</v>
+        <v>740880</v>
       </c>
       <c r="D11" t="n">
-        <v>1261883.77</v>
+        <v>2391016.32</v>
       </c>
       <c r="E11" t="n">
-        <v>67951.39999999999</v>
+        <v>127242.9</v>
       </c>
       <c r="F11" t="n">
         <v>41667</v>
       </c>
       <c r="G11" t="n">
-        <v>6660</v>
+        <v>19440</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -16657,7 +17907,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>15543</v>
+        <v>297000</v>
+      </c>
+      <c r="M11" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="12">
@@ -16668,22 +17921,22 @@
         <v>1890108</v>
       </c>
       <c r="C12" t="n">
-        <v>526680</v>
+        <v>402192</v>
       </c>
       <c r="D12" t="n">
-        <v>706751.21</v>
+        <v>1339151.62</v>
       </c>
       <c r="E12" t="n">
-        <v>79260.05</v>
+        <v>148419</v>
       </c>
       <c r="F12" t="n">
         <v>41667</v>
       </c>
       <c r="G12" t="n">
-        <v>4995</v>
+        <v>14580</v>
       </c>
       <c r="H12" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -16695,7 +17948,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>3108.6</v>
+        <v>59400</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -16706,10 +17962,10 @@
         <v>1862784</v>
       </c>
       <c r="C13" t="n">
-        <v>304920</v>
+        <v>232848</v>
       </c>
       <c r="D13" t="n">
-        <v>419103.11</v>
+        <v>794116.22</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -16718,10 +17974,10 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>2775</v>
+        <v>8100</v>
       </c>
       <c r="H13" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -16733,7 +17989,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>2543.4</v>
+        <v>48600</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -16744,10 +18003,10 @@
         <v>1928916</v>
       </c>
       <c r="C14" t="n">
-        <v>194040</v>
+        <v>148176</v>
       </c>
       <c r="D14" t="n">
-        <v>273021.93</v>
+        <v>517321.73</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -16756,7 +18015,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>7770</v>
+        <v>22680</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -16771,7 +18030,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>5086.8</v>
+        <v>97200</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -16782,10 +18044,10 @@
         <v>826848</v>
       </c>
       <c r="C15" t="n">
-        <v>166320</v>
+        <v>127008</v>
       </c>
       <c r="D15" t="n">
-        <v>237389.44</v>
+        <v>449805.31</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -16809,6 +18071,9 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16820,10 +18085,10 @@
         <v>307692</v>
       </c>
       <c r="C16" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D16" t="n">
-        <v>160506.72</v>
+        <v>304128</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -16847,6 +18112,9 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16887,6 +18155,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -16925,6 +18196,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -16963,6 +18237,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -17001,6 +18278,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -17039,6 +18319,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -17077,6 +18360,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -17115,6 +18401,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -17153,6 +18442,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -17202,6 +18494,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -17216,7 +18512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17287,13 +18583,18 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>22775.67</v>
+        <v>22707.36</v>
       </c>
       <c r="C4" t="n">
         <v>2494800</v>
@@ -17308,7 +18609,7 @@
         <v>9</v>
       </c>
       <c r="G4" t="n">
-        <v>71550</v>
+        <v>69750</v>
       </c>
       <c r="H4" t="n">
         <v>3180</v>
@@ -17320,10 +18621,13 @@
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="L4" t="n">
-        <v>154290</v>
+        <v>150180</v>
+      </c>
+      <c r="M4" t="n">
+        <v>15690</v>
       </c>
     </row>
     <row r="5">
@@ -17331,7 +18635,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>10245.51</v>
+        <v>10232.91</v>
       </c>
       <c r="C5" t="n">
         <v>755496</v>
@@ -17346,7 +18650,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>29010</v>
+        <v>28710</v>
       </c>
       <c r="H5" t="n">
         <v>180</v>
@@ -17358,10 +18662,13 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="L5" t="n">
-        <v>50040</v>
+        <v>49740</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2550</v>
       </c>
     </row>
     <row r="6">
@@ -17369,7 +18676,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>4826.88</v>
+        <v>4825.98</v>
       </c>
       <c r="C6" t="n">
         <v>268128</v>
@@ -17384,7 +18691,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>11580</v>
+        <v>11160</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -17396,10 +18703,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L6" t="n">
-        <v>19770</v>
+        <v>19620</v>
+      </c>
+      <c r="M6" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="7">
@@ -17407,7 +18717,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>2257.2</v>
+        <v>2257.11</v>
       </c>
       <c r="C7" t="n">
         <v>95760</v>
@@ -17422,7 +18732,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>4860</v>
+        <v>4620</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -17437,7 +18747,10 @@
         <v>5</v>
       </c>
       <c r="L7" t="n">
-        <v>8160</v>
+        <v>7890</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -17460,7 +18773,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>570</v>
+        <v>480</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -17476,6 +18789,9 @@
       </c>
       <c r="L8" t="n">
         <v>2250</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -17498,7 +18814,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>510</v>
+        <v>330</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -17514,6 +18830,9 @@
       </c>
       <c r="L9" t="n">
         <v>810</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -17553,6 +18872,9 @@
       <c r="L10" t="n">
         <v>300</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -17591,6 +18913,9 @@
       <c r="L11" t="n">
         <v>30</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -17629,6 +18954,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -17667,6 +18995,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -17705,6 +19036,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -17743,6 +19077,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -17781,6 +19118,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -17819,6 +19159,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -17857,6 +19200,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -17895,6 +19241,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -17933,6 +19282,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -17971,6 +19323,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -18009,6 +19364,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -18047,6 +19405,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -18085,6 +19446,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -18134,6 +19498,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -18148,7 +19516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18219,6 +19587,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -18255,6 +19628,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18263,7 +19639,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>4610.48</v>
+        <v>4604.81</v>
       </c>
       <c r="C5" t="n">
         <v>415522.8</v>
@@ -18290,10 +19666,13 @@
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>22.26</v>
+        <v>14.9</v>
       </c>
       <c r="L5" t="n">
-        <v>10508.4</v>
+        <v>10445.4</v>
+      </c>
+      <c r="M5" t="n">
+        <v>51</v>
       </c>
     </row>
     <row r="6">
@@ -18301,7 +19680,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>3861.5</v>
+        <v>3860.78</v>
       </c>
       <c r="C6" t="n">
         <v>241315.2</v>
@@ -18316,7 +19695,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>579</v>
+        <v>558</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -18328,10 +19707,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>5.85</v>
+        <v>4.06</v>
       </c>
       <c r="L6" t="n">
-        <v>7314.9</v>
+        <v>7259.4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.4</v>
       </c>
     </row>
     <row r="7">
@@ -18339,7 +19721,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>2144.34</v>
+        <v>2144.25</v>
       </c>
       <c r="C7" t="n">
         <v>95760</v>
@@ -18354,7 +19736,7 @@
         <v>0.6</v>
       </c>
       <c r="G7" t="n">
-        <v>729</v>
+        <v>693</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -18366,10 +19748,13 @@
         <v>1.4</v>
       </c>
       <c r="K7" t="n">
-        <v>4.1</v>
+        <v>3.19</v>
       </c>
       <c r="L7" t="n">
-        <v>4896</v>
+        <v>4734</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -18392,7 +19777,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>370.5</v>
+        <v>312</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -18404,10 +19789,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="L8" t="n">
         <v>1597.5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -18430,7 +19818,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>433.5</v>
+        <v>280.5</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -18442,10 +19830,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="L9" t="n">
         <v>656.1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -18485,6 +19876,9 @@
       <c r="L10" t="n">
         <v>267</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -18523,6 +19917,9 @@
       <c r="L11" t="n">
         <v>30</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -18561,6 +19958,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -18599,6 +19999,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -18637,6 +20040,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -18675,6 +20081,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -18713,6 +20122,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -18751,6 +20163,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -18789,6 +20204,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -18827,6 +20245,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -18865,6 +20286,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -18903,6 +20327,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -18941,6 +20368,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -18979,6 +20409,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -19017,6 +20450,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -19066,6 +20502,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -19080,7 +20520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19151,6 +20591,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -19187,6 +20632,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19195,16 +20643,16 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>10143054.9</v>
+        <v>10130580.9</v>
       </c>
       <c r="C5" t="n">
-        <v>22853754</v>
+        <v>17451957.6</v>
       </c>
       <c r="D5" t="n">
-        <v>19909614.69</v>
+        <v>37724721.41</v>
       </c>
       <c r="E5" t="n">
-        <v>3383558.39</v>
+        <v>6335907.75</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -19213,19 +20661,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>17926.92</v>
+        <v>369360</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>17499.9</v>
+        <v>7283.4</v>
       </c>
       <c r="K5" t="n">
-        <v>474894.84</v>
+        <v>723241.62</v>
       </c>
       <c r="L5" t="n">
-        <v>98989.13</v>
+        <v>1880172</v>
+      </c>
+      <c r="M5" t="n">
+        <v>15300</v>
       </c>
     </row>
     <row r="6">
@@ -19233,22 +20684,22 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>8495308.800000001</v>
+        <v>8493724.800000001</v>
       </c>
       <c r="C6" t="n">
-        <v>13272336</v>
+        <v>10135238.4</v>
       </c>
       <c r="D6" t="n">
-        <v>10823128.64</v>
+        <v>20507655.17</v>
       </c>
       <c r="E6" t="n">
-        <v>1541259.72</v>
+        <v>2886097.5</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>10711.5</v>
+        <v>30132</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -19260,10 +20711,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>124803.9</v>
+        <v>196943.14</v>
       </c>
       <c r="L6" t="n">
-        <v>68906.36</v>
+        <v>1306692</v>
+      </c>
+      <c r="M6" t="n">
+        <v>720</v>
       </c>
     </row>
     <row r="7">
@@ -19271,22 +20725,22 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>4717548</v>
+        <v>4717359.9</v>
       </c>
       <c r="C7" t="n">
-        <v>5266800</v>
+        <v>4021920</v>
       </c>
       <c r="D7" t="n">
-        <v>4864156.15</v>
+        <v>9216599.039999999</v>
       </c>
       <c r="E7" t="n">
-        <v>881726.58</v>
+        <v>1651083.75</v>
       </c>
       <c r="F7" t="n">
         <v>25000.2</v>
       </c>
       <c r="G7" t="n">
-        <v>13486.5</v>
+        <v>37422</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -19295,13 +20749,16 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>81666.2</v>
+        <v>33989.2</v>
       </c>
       <c r="K7" t="n">
-        <v>87469.39999999999</v>
+        <v>154893.64</v>
       </c>
       <c r="L7" t="n">
-        <v>46120.32</v>
+        <v>852120</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -19312,19 +20769,19 @@
         <v>2086128</v>
       </c>
       <c r="C8" t="n">
-        <v>1275120</v>
+        <v>973728</v>
       </c>
       <c r="D8" t="n">
-        <v>1358528.88</v>
+        <v>2574139.39</v>
       </c>
       <c r="E8" t="n">
-        <v>528770.64</v>
+        <v>990153.45</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>6854.25</v>
+        <v>16848</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -19336,10 +20793,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>38401.2</v>
+        <v>71474.42999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>15048.45</v>
+        <v>287550</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -19350,19 +20810,19 @@
         <v>793782</v>
       </c>
       <c r="C9" t="n">
-        <v>970200</v>
+        <v>740880</v>
       </c>
       <c r="D9" t="n">
-        <v>1127760.34</v>
+        <v>2136879.36</v>
       </c>
       <c r="E9" t="n">
-        <v>443889.43</v>
+        <v>831208.5</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>8019.75</v>
+        <v>15147</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -19374,10 +20834,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>42668</v>
+        <v>77980.94</v>
       </c>
       <c r="L9" t="n">
-        <v>6180.46</v>
+        <v>118098</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -19388,10 +20851,10 @@
         <v>375210</v>
       </c>
       <c r="C10" t="n">
-        <v>388080</v>
+        <v>296352</v>
       </c>
       <c r="D10" t="n">
-        <v>488742.96</v>
+        <v>926069.76</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -19400,7 +20863,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>555</v>
+        <v>1620</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -19415,7 +20878,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2515.14</v>
+        <v>48060</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -19426,10 +20892,10 @@
         <v>171270</v>
       </c>
       <c r="C11" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D11" t="n">
-        <v>144215.29</v>
+        <v>273259.01</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -19453,7 +20919,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>282.6</v>
+        <v>5400</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -19464,19 +20933,19 @@
         <v>129690</v>
       </c>
       <c r="C12" t="n">
-        <v>138600</v>
+        <v>105840</v>
       </c>
       <c r="D12" t="n">
-        <v>185987.16</v>
+        <v>352408.32</v>
       </c>
       <c r="E12" t="n">
-        <v>79260.05</v>
+        <v>148419</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>555</v>
+        <v>1620</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -19491,6 +20960,9 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19502,10 +20974,10 @@
         <v>55440</v>
       </c>
       <c r="C13" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D13" t="n">
-        <v>114300.85</v>
+        <v>216577.15</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -19529,6 +21001,9 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19569,6 +21044,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -19607,6 +21085,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -19645,6 +21126,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -19683,6 +21167,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -19721,6 +21208,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -19759,6 +21249,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -19797,6 +21290,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -19835,6 +21331,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -19873,6 +21372,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -19911,6 +21413,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -19949,6 +21454,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -19998,6 +21506,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -20012,7 +21524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20083,6 +21595,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -20104,10 +21621,10 @@
         <v>15</v>
       </c>
       <c r="G4" t="n">
-        <v>59340</v>
+        <v>59400</v>
       </c>
       <c r="H4" t="n">
-        <v>17970</v>
+        <v>18000</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -20119,7 +21636,10 @@
         <v>99</v>
       </c>
       <c r="L4" t="n">
-        <v>172140</v>
+        <v>172260</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -20142,10 +21662,10 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>19800</v>
+        <v>19950</v>
       </c>
       <c r="H5" t="n">
-        <v>1800</v>
+        <v>1830</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -20158,6 +21678,9 @@
       </c>
       <c r="L5" t="n">
         <v>42840</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -20183,7 +21706,7 @@
         <v>930</v>
       </c>
       <c r="H6" t="n">
-        <v>420</v>
+        <v>390</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -20196,6 +21719,9 @@
       </c>
       <c r="L6" t="n">
         <v>4590</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -20218,10 +21744,10 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="H7" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -20234,6 +21760,9 @@
       </c>
       <c r="L7" t="n">
         <v>1440</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -20273,6 +21802,9 @@
       <c r="L8" t="n">
         <v>300</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -20311,6 +21843,9 @@
       <c r="L9" t="n">
         <v>120</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -20349,6 +21884,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -20387,6 +21925,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -20425,6 +21966,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -20463,6 +22007,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -20501,6 +22048,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -20539,6 +22089,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -20577,6 +22130,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -20615,6 +22171,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -20653,6 +22212,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -20691,6 +22253,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -20729,6 +22294,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -20767,6 +22335,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -20805,6 +22376,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -20843,6 +22417,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -20881,6 +22458,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -20930,6 +22510,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -20944,7 +22528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21015,6 +22599,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -21051,6 +22640,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21077,7 +22669,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>648</v>
+        <v>658.8</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -21086,10 +22678,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>11.34</v>
+        <v>8.94</v>
       </c>
       <c r="L5" t="n">
         <v>8996.4</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -21115,7 +22710,7 @@
         <v>46.5</v>
       </c>
       <c r="H6" t="n">
-        <v>239.4</v>
+        <v>222.3</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -21124,10 +22719,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="L6" t="n">
         <v>1698.3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -21150,10 +22748,10 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="H7" t="n">
-        <v>109.5</v>
+        <v>131.4</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -21166,6 +22764,9 @@
       </c>
       <c r="L7" t="n">
         <v>864</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -21205,6 +22806,9 @@
       <c r="L8" t="n">
         <v>213</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -21243,6 +22847,9 @@
       <c r="L9" t="n">
         <v>97.2</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -21281,6 +22888,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -21319,6 +22929,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -21357,6 +22970,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -21395,6 +23011,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -21433,6 +23052,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -21471,6 +23093,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -21509,6 +23134,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -21547,6 +23175,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -21585,6 +23216,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -21623,6 +23257,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -21661,6 +23298,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -21699,6 +23339,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -21737,6 +23380,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -21775,6 +23421,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -21813,6 +23462,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -21862,6 +23514,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -21876,7 +23532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21947,6 +23603,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -21983,6 +23644,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21994,13 +23658,13 @@
         <v>4919745.6</v>
       </c>
       <c r="C5" t="n">
-        <v>14956326</v>
+        <v>11421194.4</v>
       </c>
       <c r="D5" t="n">
-        <v>13029574.39</v>
+        <v>24688426.75</v>
       </c>
       <c r="E5" t="n">
-        <v>969343.75</v>
+        <v>1815151.95</v>
       </c>
       <c r="F5" t="n">
         <v>2500.02</v>
@@ -22009,7 +23673,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>179269.2</v>
+        <v>3755160</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -22018,10 +23682,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>241927.56</v>
+        <v>433944.97</v>
       </c>
       <c r="L5" t="n">
-        <v>84746.09</v>
+        <v>1619352</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -22032,22 +23699,22 @@
         <v>422136</v>
       </c>
       <c r="C6" t="n">
-        <v>2744280</v>
+        <v>2095632</v>
       </c>
       <c r="D6" t="n">
-        <v>2237864.94</v>
+        <v>4240304.64</v>
       </c>
       <c r="E6" t="n">
-        <v>196160.33</v>
+        <v>367321.5</v>
       </c>
       <c r="F6" t="n">
         <v>4166.7</v>
       </c>
       <c r="G6" t="n">
-        <v>860.25</v>
+        <v>2511</v>
       </c>
       <c r="H6" t="n">
-        <v>66230.00999999999</v>
+        <v>1267110</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -22056,10 +23723,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>27734.2</v>
+        <v>49235.78</v>
       </c>
       <c r="L6" t="n">
-        <v>15997.99</v>
+        <v>305694</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -22070,10 +23740,10 @@
         <v>84456.89999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>221760</v>
+        <v>169344</v>
       </c>
       <c r="D7" t="n">
-        <v>204806.57</v>
+        <v>388067.33</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -22082,10 +23752,10 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>249.75</v>
+        <v>972</v>
       </c>
       <c r="H7" t="n">
-        <v>30293.18</v>
+        <v>748980</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -22097,7 +23767,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>8138.88</v>
+        <v>155520</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -22108,10 +23781,10 @@
         <v>39006</v>
       </c>
       <c r="C8" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D8" t="n">
-        <v>59066.47</v>
+        <v>111919.1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -22123,7 +23796,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>14109.15</v>
+        <v>290700</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -22135,7 +23808,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2006.46</v>
+        <v>38340</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -22173,7 +23849,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>915.62</v>
+        <v>17496</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -22213,6 +23892,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -22251,6 +23933,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -22289,6 +23974,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -22327,6 +24015,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -22365,6 +24056,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -22403,6 +24097,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -22441,6 +24138,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -22479,6 +24179,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -22517,6 +24220,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -22555,6 +24261,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -22593,6 +24302,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -22631,6 +24343,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -22669,6 +24384,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -22707,6 +24425,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -22745,6 +24466,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -22794,6 +24518,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>

--- a/risk/Risk_Analysis_T3_5yrs_Present_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_5yrs_Present_Perfect.xlsx
@@ -549,7 +549,7 @@
         <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>468</v>
+        <v>159</v>
       </c>
       <c r="L4" t="n">
         <v>716010</v>
@@ -590,7 +590,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="L5" t="n">
         <v>229410</v>
@@ -631,7 +631,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
         <v>80370</v>
@@ -672,7 +672,7 @@
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>42330</v>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>17100</v>
@@ -754,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>5910</v>
@@ -1553,7 +1553,7 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
         <v>59760</v>
@@ -1594,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="L5" t="n">
         <v>36390</v>
@@ -1635,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>21450</v>
@@ -1676,7 +1676,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>8850</v>
@@ -1758,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>960</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>9.6</v>
+        <v>2.32</v>
       </c>
       <c r="L5" t="n">
         <v>7641.9</v>
@@ -2639,7 +2639,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>6.08</v>
+        <v>0.51</v>
       </c>
       <c r="L6" t="n">
         <v>7936.5</v>
@@ -2680,7 +2680,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>5310</v>
@@ -2762,7 +2762,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>777.6</v>
@@ -3602,7 +3602,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>466089.04</v>
+        <v>112504.25</v>
       </c>
       <c r="L5" t="n">
         <v>1375542</v>
@@ -3643,7 +3643,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>295414.7</v>
+        <v>24617.89</v>
       </c>
       <c r="L6" t="n">
         <v>1428570</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>92936.17999999999</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>955800</v>
@@ -3766,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>116971.4</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>139968</v>
@@ -4565,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
         <v>33450</v>
@@ -4606,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
         <v>4170</v>
@@ -5610,7 +5610,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1.32</v>
+        <v>0.66</v>
       </c>
       <c r="L5" t="n">
         <v>875.7</v>
@@ -6614,7 +6614,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>64288.14</v>
+        <v>32144.07</v>
       </c>
       <c r="L5" t="n">
         <v>157626</v>
@@ -7577,7 +7577,7 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
         <v>10860</v>
@@ -7618,7 +7618,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>1500</v>
@@ -7659,7 +7659,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -8622,7 +8622,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>315</v>
@@ -8663,7 +8663,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -9626,7 +9626,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>80360.17999999999</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>56700</v>
@@ -9667,7 +9667,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>24617.89</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -10589,7 +10589,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>150</v>
+        <v>72</v>
       </c>
       <c r="L4" t="n">
         <v>164370</v>
@@ -10630,7 +10630,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="L5" t="n">
         <v>54660</v>
@@ -10671,7 +10671,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>15180</v>
@@ -11634,7 +11634,7 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>43.03</v>
+        <v>9.93</v>
       </c>
       <c r="L5" t="n">
         <v>48176.1</v>
@@ -11675,7 +11675,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>14.2</v>
+        <v>1.01</v>
       </c>
       <c r="L6" t="n">
         <v>29736.9</v>
@@ -11716,7 +11716,7 @@
         <v>1.4</v>
       </c>
       <c r="K7" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>25398</v>
@@ -11757,7 +11757,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>12141</v>
@@ -11798,7 +11798,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>4.82</v>
+        <v>1.61</v>
       </c>
       <c r="L9" t="n">
         <v>4787.1</v>
@@ -12638,7 +12638,7 @@
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>5.96</v>
+        <v>1.99</v>
       </c>
       <c r="L5" t="n">
         <v>11478.6</v>
@@ -12679,7 +12679,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>5616.6</v>
@@ -13642,7 +13642,7 @@
         <v>7283.4</v>
       </c>
       <c r="K5" t="n">
-        <v>289296.65</v>
+        <v>96432.22</v>
       </c>
       <c r="L5" t="n">
         <v>2066148</v>
@@ -13683,7 +13683,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>98471.57000000001</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>1010988</v>
@@ -14605,7 +14605,7 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="L4" t="n">
         <v>89490</v>
@@ -17658,7 +17658,7 @@
         <v>14566.8</v>
       </c>
       <c r="K5" t="n">
-        <v>2089364.68</v>
+        <v>482161.08</v>
       </c>
       <c r="L5" t="n">
         <v>8671698</v>
@@ -17699,7 +17699,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>689300.98</v>
+        <v>49235.78</v>
       </c>
       <c r="L6" t="n">
         <v>5352642</v>
@@ -17740,7 +17740,7 @@
         <v>33989.2</v>
       </c>
       <c r="K7" t="n">
-        <v>247829.82</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>4571640</v>
@@ -17781,7 +17781,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>107211.65</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>2185380</v>
@@ -17822,7 +17822,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>233942.81</v>
+        <v>77980.94</v>
       </c>
       <c r="L9" t="n">
         <v>861678</v>
@@ -18621,7 +18621,7 @@
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="L4" t="n">
         <v>150180</v>
@@ -18662,7 +18662,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="L5" t="n">
         <v>49740</v>
@@ -18703,7 +18703,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>19620</v>
@@ -18744,7 +18744,7 @@
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>7890</v>
@@ -18785,7 +18785,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>2250</v>
@@ -18826,7 +18826,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>810</v>
@@ -19666,7 +19666,7 @@
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>14.9</v>
+        <v>1.99</v>
       </c>
       <c r="L5" t="n">
         <v>10445.4</v>
@@ -19707,7 +19707,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>4.06</v>
+        <v>0.51</v>
       </c>
       <c r="L6" t="n">
         <v>7259.4</v>
@@ -19748,7 +19748,7 @@
         <v>1.4</v>
       </c>
       <c r="K7" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>4734</v>
@@ -19789,7 +19789,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>1597.5</v>
@@ -19830,7 +19830,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1.61</v>
+        <v>0.8</v>
       </c>
       <c r="L9" t="n">
         <v>656.1</v>
@@ -20670,7 +20670,7 @@
         <v>7283.4</v>
       </c>
       <c r="K5" t="n">
-        <v>723241.62</v>
+        <v>96432.22</v>
       </c>
       <c r="L5" t="n">
         <v>1880172</v>
@@ -20711,7 +20711,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>196943.14</v>
+        <v>24617.89</v>
       </c>
       <c r="L6" t="n">
         <v>1306692</v>
@@ -20752,7 +20752,7 @@
         <v>33989.2</v>
       </c>
       <c r="K7" t="n">
-        <v>154893.64</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>852120</v>
@@ -20793,7 +20793,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>71474.42999999999</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>287550</v>
@@ -20834,7 +20834,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>77980.94</v>
+        <v>38990.47</v>
       </c>
       <c r="L9" t="n">
         <v>118098</v>
@@ -21633,7 +21633,7 @@
         <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>99</v>
+        <v>31</v>
       </c>
       <c r="L4" t="n">
         <v>172260</v>
@@ -21674,7 +21674,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="L5" t="n">
         <v>42840</v>
@@ -21715,7 +21715,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>4590</v>
@@ -22678,7 +22678,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>8.94</v>
+        <v>2.98</v>
       </c>
       <c r="L5" t="n">
         <v>8996.4</v>
@@ -22719,7 +22719,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>1698.3</v>
@@ -23682,7 +23682,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>433944.97</v>
+        <v>144648.32</v>
       </c>
       <c r="L5" t="n">
         <v>1619352</v>
@@ -23723,7 +23723,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>49235.78</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>305694</v>

--- a/risk/Risk_Analysis_T3_5yrs_Present_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_5yrs_Present_Perfect.xlsx
@@ -560,7 +560,7 @@
         <v>270660</v>
       </c>
       <c r="H4" t="n">
-        <v>40230</v>
+        <v>51360</v>
       </c>
       <c r="I4" t="n">
         <v>4</v>
@@ -572,22 +572,22 @@
         <v>159</v>
       </c>
       <c r="L4" t="n">
-        <v>716010</v>
+        <v>919050</v>
       </c>
       <c r="M4" t="n">
-        <v>38100</v>
+        <v>70920</v>
       </c>
       <c r="N4" t="n">
-        <v>34140</v>
+        <v>48180</v>
       </c>
       <c r="O4" t="n">
-        <v>233160</v>
+        <v>306000</v>
       </c>
       <c r="P4" t="n">
-        <v>95040</v>
+        <v>77640</v>
       </c>
       <c r="Q4" t="n">
-        <v>111840.72</v>
+        <v>1158994.57</v>
       </c>
     </row>
     <row r="5">
@@ -613,7 +613,7 @@
         <v>95550</v>
       </c>
       <c r="H5" t="n">
-        <v>6180</v>
+        <v>9060</v>
       </c>
       <c r="I5" t="n">
         <v>2</v>
@@ -625,22 +625,22 @@
         <v>30</v>
       </c>
       <c r="L5" t="n">
-        <v>229410</v>
+        <v>300900</v>
       </c>
       <c r="M5" t="n">
-        <v>18060</v>
+        <v>46470</v>
       </c>
       <c r="N5" t="n">
-        <v>6960</v>
+        <v>11850</v>
       </c>
       <c r="O5" t="n">
-        <v>84570</v>
+        <v>111660</v>
       </c>
       <c r="P5" t="n">
-        <v>103050</v>
+        <v>104130</v>
       </c>
       <c r="Q5" t="n">
-        <v>40220.42</v>
+        <v>416800.29</v>
       </c>
     </row>
     <row r="6">
@@ -666,7 +666,7 @@
         <v>31650</v>
       </c>
       <c r="H6" t="n">
-        <v>3810</v>
+        <v>4440</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -678,22 +678,22 @@
         <v>2</v>
       </c>
       <c r="L6" t="n">
-        <v>80370</v>
+        <v>113940</v>
       </c>
       <c r="M6" t="n">
-        <v>6870</v>
+        <v>33150</v>
       </c>
       <c r="N6" t="n">
-        <v>960</v>
+        <v>2970</v>
       </c>
       <c r="O6" t="n">
-        <v>33060</v>
+        <v>47370</v>
       </c>
       <c r="P6" t="n">
-        <v>98100</v>
+        <v>111570</v>
       </c>
       <c r="Q6" t="n">
-        <v>22416.2</v>
+        <v>232296.9</v>
       </c>
     </row>
     <row r="7">
@@ -719,7 +719,7 @@
         <v>16560</v>
       </c>
       <c r="H7" t="n">
-        <v>240</v>
+        <v>810</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -731,22 +731,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>42330</v>
+        <v>77730</v>
       </c>
       <c r="M7" t="n">
-        <v>3900</v>
+        <v>22290</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>6120</v>
+        <v>14970</v>
       </c>
       <c r="P7" t="n">
-        <v>85110</v>
+        <v>109050</v>
       </c>
       <c r="Q7" t="n">
-        <v>14540.92</v>
+        <v>150686.17</v>
       </c>
     </row>
     <row r="8">
@@ -772,7 +772,7 @@
         <v>12540</v>
       </c>
       <c r="H8" t="n">
-        <v>120</v>
+        <v>450</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -784,22 +784,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>17100</v>
+        <v>47970</v>
       </c>
       <c r="M8" t="n">
-        <v>1230</v>
+        <v>17190</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>810</v>
+        <v>2160</v>
       </c>
       <c r="P8" t="n">
-        <v>62520</v>
+        <v>103560</v>
       </c>
       <c r="Q8" t="n">
-        <v>8730.58</v>
+        <v>90474.14999999999</v>
       </c>
     </row>
     <row r="9">
@@ -825,7 +825,7 @@
         <v>2490</v>
       </c>
       <c r="H9" t="n">
-        <v>90</v>
+        <v>210</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -837,22 +837,22 @@
         <v>2</v>
       </c>
       <c r="L9" t="n">
-        <v>5910</v>
+        <v>34500</v>
       </c>
       <c r="M9" t="n">
-        <v>390</v>
+        <v>8370</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="P9" t="n">
-        <v>46830</v>
+        <v>80340</v>
       </c>
       <c r="Q9" t="n">
-        <v>4600.26</v>
+        <v>47672.09</v>
       </c>
     </row>
     <row r="10">
@@ -878,7 +878,7 @@
         <v>810</v>
       </c>
       <c r="H10" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -890,10 +890,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2880</v>
+        <v>23910</v>
       </c>
       <c r="M10" t="n">
-        <v>240</v>
+        <v>2970</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -902,10 +902,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>35820</v>
+        <v>63960</v>
       </c>
       <c r="Q10" t="n">
-        <v>2356.55</v>
+        <v>24420.65</v>
       </c>
     </row>
     <row r="11">
@@ -943,10 +943,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1650</v>
+        <v>7170</v>
       </c>
       <c r="M11" t="n">
-        <v>30</v>
+        <v>3210</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -955,10 +955,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>19320</v>
+        <v>42540</v>
       </c>
       <c r="Q11" t="n">
-        <v>1392.77</v>
+        <v>14433.12</v>
       </c>
     </row>
     <row r="12">
@@ -996,10 +996,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>330</v>
+        <v>3990</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3630</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1008,10 +1008,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>14490</v>
+        <v>28560</v>
       </c>
       <c r="Q12" t="n">
-        <v>1065.33</v>
+        <v>11039.95</v>
       </c>
     </row>
     <row r="13">
@@ -1037,7 +1037,7 @@
         <v>150</v>
       </c>
       <c r="H13" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1049,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>270</v>
+        <v>1290</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>660</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2730</v>
+        <v>6480</v>
       </c>
       <c r="Q13" t="n">
-        <v>1049.93</v>
+        <v>10880.35</v>
       </c>
     </row>
     <row r="14">
@@ -1102,22 +1102,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
+        <v>1410</v>
+      </c>
+      <c r="M14" t="n">
+        <v>150</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
         <v>540</v>
       </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>240</v>
-      </c>
       <c r="Q14" t="n">
-        <v>1087.21</v>
+        <v>11266.62</v>
       </c>
     </row>
     <row r="15">
@@ -1155,10 +1155,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -1170,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>466.04</v>
+        <v>4829.54</v>
       </c>
     </row>
     <row r="16">
@@ -1208,7 +1208,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -1223,7 +1223,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>173.43</v>
+        <v>1797.2</v>
       </c>
     </row>
     <row r="17">
@@ -1261,7 +1261,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -1276,7 +1276,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>37.83</v>
+        <v>392.05</v>
       </c>
     </row>
     <row r="18">
@@ -1314,7 +1314,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1329,7 +1329,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.68</v>
+        <v>38.16</v>
       </c>
     </row>
     <row r="19">
@@ -1382,7 +1382,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.22</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="20">
@@ -1852,7 +1852,7 @@
         <v>25410</v>
       </c>
       <c r="H4" t="n">
-        <v>2430</v>
+        <v>3840</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1864,22 +1864,22 @@
         <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>59760</v>
+        <v>78660</v>
       </c>
       <c r="M4" t="n">
-        <v>7290</v>
+        <v>9990</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>660</v>
       </c>
       <c r="O4" t="n">
-        <v>450</v>
+        <v>540</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1405.48</v>
+        <v>159288.3</v>
       </c>
     </row>
     <row r="5">
@@ -1905,7 +1905,7 @@
         <v>14280</v>
       </c>
       <c r="H5" t="n">
-        <v>1950</v>
+        <v>1860</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -1917,22 +1917,22 @@
         <v>7</v>
       </c>
       <c r="L5" t="n">
-        <v>36390</v>
+        <v>42840</v>
       </c>
       <c r="M5" t="n">
-        <v>8490</v>
+        <v>13170</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1187.16</v>
+        <v>134545.14</v>
       </c>
     </row>
     <row r="6">
@@ -1958,7 +1958,7 @@
         <v>7020</v>
       </c>
       <c r="H6" t="n">
-        <v>3330</v>
+        <v>3780</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1970,10 +1970,10 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>21450</v>
+        <v>28230</v>
       </c>
       <c r="M6" t="n">
-        <v>3180</v>
+        <v>7770</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1212.19</v>
+        <v>137381.76</v>
       </c>
     </row>
     <row r="7">
@@ -2011,7 +2011,7 @@
         <v>3630</v>
       </c>
       <c r="H7" t="n">
-        <v>90</v>
+        <v>450</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -2023,10 +2023,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>8850</v>
+        <v>15180</v>
       </c>
       <c r="M7" t="n">
-        <v>1980</v>
+        <v>3960</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1067.53</v>
+        <v>120986.28</v>
       </c>
     </row>
     <row r="8">
@@ -2076,10 +2076,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2910</v>
+        <v>6480</v>
       </c>
       <c r="M8" t="n">
-        <v>600</v>
+        <v>2010</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>676.62</v>
+        <v>76683.60000000001</v>
       </c>
     </row>
     <row r="9">
@@ -2117,7 +2117,7 @@
         <v>870</v>
       </c>
       <c r="H9" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -2129,10 +2129,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>960</v>
+        <v>2340</v>
       </c>
       <c r="M9" t="n">
-        <v>150</v>
+        <v>1050</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -2144,7 +2144,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>291.33</v>
+        <v>33017.4</v>
       </c>
     </row>
     <row r="10">
@@ -2182,10 +2182,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>660</v>
+        <v>1050</v>
       </c>
       <c r="M10" t="n">
-        <v>60</v>
+        <v>720</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -2197,7 +2197,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>131.3</v>
+        <v>14880.78</v>
       </c>
     </row>
     <row r="11">
@@ -2235,10 +2235,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1170</v>
+        <v>2400</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -2250,7 +2250,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>88.29000000000001</v>
+        <v>10006.2</v>
       </c>
     </row>
     <row r="12">
@@ -2288,10 +2288,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>240</v>
+        <v>1290</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>660</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -2303,7 +2303,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>72.70999999999999</v>
+        <v>8240.58</v>
       </c>
     </row>
     <row r="13">
@@ -2329,7 +2329,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -2341,11 +2341,11 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
+        <v>420</v>
+      </c>
+      <c r="M13" t="n">
         <v>90</v>
       </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
@@ -2356,7 +2356,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>85.48</v>
+        <v>9687.959999999999</v>
       </c>
     </row>
     <row r="14">
@@ -2394,10 +2394,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>780</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>95.93000000000001</v>
+        <v>10872.18</v>
       </c>
     </row>
     <row r="15">
@@ -2447,10 +2447,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2462,7 +2462,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>37.99</v>
+        <v>4305.42</v>
       </c>
     </row>
     <row r="16">
@@ -2500,7 +2500,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>28.86</v>
+        <v>3271.14</v>
       </c>
     </row>
     <row r="17">
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.62</v>
+        <v>70.38</v>
       </c>
     </row>
     <row r="18">
@@ -2606,7 +2606,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2621,7 +2621,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.51</v>
+        <v>58.14</v>
       </c>
     </row>
     <row r="19">
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>702</v>
+        <v>669.6</v>
       </c>
       <c r="I5" t="n">
         <v>0.33</v>
@@ -3209,22 +3209,22 @@
         <v>2.32</v>
       </c>
       <c r="L5" t="n">
-        <v>7641.9</v>
+        <v>8996.4</v>
       </c>
       <c r="M5" t="n">
-        <v>169.8</v>
+        <v>263.4</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>4.5</v>
+        <v>13.5</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>59.36</v>
+        <v>6727.26</v>
       </c>
     </row>
     <row r="6">
@@ -3250,7 +3250,7 @@
         <v>351</v>
       </c>
       <c r="H6" t="n">
-        <v>1898.1</v>
+        <v>2154.6</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -3262,10 +3262,10 @@
         <v>0.51</v>
       </c>
       <c r="L6" t="n">
-        <v>7936.5</v>
+        <v>10445.1</v>
       </c>
       <c r="M6" t="n">
-        <v>254.4</v>
+        <v>621.6</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -3277,7 +3277,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>909.14</v>
+        <v>103036.32</v>
       </c>
     </row>
     <row r="7">
@@ -3303,7 +3303,7 @@
         <v>544.5</v>
       </c>
       <c r="H7" t="n">
-        <v>65.7</v>
+        <v>328.5</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3315,10 +3315,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>5310</v>
+        <v>9108</v>
       </c>
       <c r="M7" t="n">
-        <v>693</v>
+        <v>1386</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -3330,7 +3330,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>854.02</v>
+        <v>96789.02</v>
       </c>
     </row>
     <row r="8">
@@ -3368,10 +3368,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2066.1</v>
+        <v>4600.8</v>
       </c>
       <c r="M8" t="n">
-        <v>330</v>
+        <v>1105.5</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>642.79</v>
+        <v>72849.42</v>
       </c>
     </row>
     <row r="9">
@@ -3409,7 +3409,7 @@
         <v>739.5</v>
       </c>
       <c r="H9" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -3421,10 +3421,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>777.6</v>
+        <v>1895.4</v>
       </c>
       <c r="M9" t="n">
-        <v>105</v>
+        <v>735</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -3436,7 +3436,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>282.59</v>
+        <v>32026.88</v>
       </c>
     </row>
     <row r="10">
@@ -3474,10 +3474,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>587.4</v>
+        <v>934.5</v>
       </c>
       <c r="M10" t="n">
-        <v>51</v>
+        <v>612</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -3489,7 +3489,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>131.3</v>
+        <v>14880.78</v>
       </c>
     </row>
     <row r="11">
@@ -3527,10 +3527,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1170</v>
+        <v>2400</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1620</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>88.29000000000001</v>
+        <v>10006.2</v>
       </c>
     </row>
     <row r="12">
@@ -3580,10 +3580,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>240</v>
+        <v>1290</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>627</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -3595,7 +3595,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>72.70999999999999</v>
+        <v>8240.58</v>
       </c>
     </row>
     <row r="13">
@@ -3621,7 +3621,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -3633,11 +3633,11 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
+        <v>420</v>
+      </c>
+      <c r="M13" t="n">
         <v>90</v>
       </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
@@ -3648,7 +3648,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>85.48</v>
+        <v>9687.959999999999</v>
       </c>
     </row>
     <row r="14">
@@ -3686,10 +3686,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>780</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>95.93000000000001</v>
+        <v>10872.18</v>
       </c>
     </row>
     <row r="15">
@@ -3739,10 +3739,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>37.99</v>
+        <v>4305.42</v>
       </c>
     </row>
     <row r="16">
@@ -3792,7 +3792,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -3807,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>28.86</v>
+        <v>3271.14</v>
       </c>
     </row>
     <row r="17">
@@ -3845,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.62</v>
+        <v>70.38</v>
       </c>
     </row>
     <row r="18">
@@ -3898,7 +3898,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -3913,7 +3913,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.51</v>
+        <v>58.14</v>
       </c>
     </row>
     <row r="19">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4001400</v>
+        <v>3816720</v>
       </c>
       <c r="I5" t="n">
         <v>64288.14</v>
@@ -4501,22 +4501,22 @@
         <v>112504.25</v>
       </c>
       <c r="L5" t="n">
-        <v>1375542</v>
+        <v>1619352</v>
       </c>
       <c r="M5" t="n">
-        <v>59430</v>
+        <v>92190</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>765</v>
+        <v>2295</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>35614.89</v>
+        <v>4036354.2</v>
       </c>
     </row>
     <row r="6">
@@ -4542,7 +4542,7 @@
         <v>18954</v>
       </c>
       <c r="H6" t="n">
-        <v>10819170</v>
+        <v>12281220</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -4554,10 +4554,10 @@
         <v>24617.89</v>
       </c>
       <c r="L6" t="n">
-        <v>1428570</v>
+        <v>1880118</v>
       </c>
       <c r="M6" t="n">
-        <v>89040</v>
+        <v>217560</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -4569,7 +4569,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>545486.4</v>
+        <v>61821792</v>
       </c>
     </row>
     <row r="7">
@@ -4595,7 +4595,7 @@
         <v>29403</v>
       </c>
       <c r="H7" t="n">
-        <v>374490</v>
+        <v>1872450</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -4607,10 +4607,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>955800</v>
+        <v>1639440</v>
       </c>
       <c r="M7" t="n">
-        <v>242550</v>
+        <v>485100</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -4622,7 +4622,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>512412.48</v>
+        <v>58073414.4</v>
       </c>
     </row>
     <row r="8">
@@ -4660,10 +4660,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>371898</v>
+        <v>828144</v>
       </c>
       <c r="M8" t="n">
-        <v>115500</v>
+        <v>386925</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -4675,7 +4675,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>385673.4</v>
+        <v>43709652</v>
       </c>
     </row>
     <row r="9">
@@ -4701,7 +4701,7 @@
         <v>39933</v>
       </c>
       <c r="H9" t="n">
-        <v>342000</v>
+        <v>1026000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -4713,10 +4713,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>139968</v>
+        <v>341172</v>
       </c>
       <c r="M9" t="n">
-        <v>36750</v>
+        <v>257250</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -4728,7 +4728,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>169554.06</v>
+        <v>19216126.8</v>
       </c>
     </row>
     <row r="10">
@@ -4766,10 +4766,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>105732</v>
+        <v>168210</v>
       </c>
       <c r="M10" t="n">
-        <v>17850</v>
+        <v>214200</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -4781,7 +4781,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>78780.60000000001</v>
+        <v>8928468</v>
       </c>
     </row>
     <row r="11">
@@ -4819,10 +4819,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>210600</v>
+        <v>432000</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>567000</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -4834,7 +4834,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>52974</v>
+        <v>6003720</v>
       </c>
     </row>
     <row r="12">
@@ -4872,10 +4872,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>43200</v>
+        <v>232200</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>219450</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -4887,7 +4887,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>43626.6</v>
+        <v>4944348</v>
       </c>
     </row>
     <row r="13">
@@ -4913,7 +4913,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>171000</v>
+        <v>513000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -4925,10 +4925,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>16200</v>
+        <v>75600</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -4940,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>51289.2</v>
+        <v>5812776</v>
       </c>
     </row>
     <row r="14">
@@ -4978,10 +4978,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>140400</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>52500</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>57558.6</v>
+        <v>6523308</v>
       </c>
     </row>
     <row r="15">
@@ -5031,10 +5031,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>172800</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>84000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -5046,7 +5046,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>22793.4</v>
+        <v>2583252</v>
       </c>
     </row>
     <row r="16">
@@ -5084,7 +5084,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>64800</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -5099,7 +5099,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>17317.8</v>
+        <v>1962684</v>
       </c>
     </row>
     <row r="17">
@@ -5137,7 +5137,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -5152,7 +5152,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>372.6</v>
+        <v>42228</v>
       </c>
     </row>
     <row r="18">
@@ -5190,7 +5190,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -5205,7 +5205,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>307.8</v>
+        <v>34884</v>
       </c>
     </row>
     <row r="19">
@@ -5728,7 +5728,7 @@
         <v>9420</v>
       </c>
       <c r="H4" t="n">
-        <v>480</v>
+        <v>1710</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -5740,22 +5740,22 @@
         <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>33450</v>
+        <v>53280</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1860</v>
+        <v>2340</v>
       </c>
       <c r="O4" t="n">
-        <v>11100</v>
+        <v>15570</v>
       </c>
       <c r="P4" t="n">
-        <v>5910</v>
+        <v>12300</v>
       </c>
       <c r="Q4" t="n">
-        <v>5664.34</v>
+        <v>29812.32</v>
       </c>
     </row>
     <row r="5">
@@ -5781,7 +5781,7 @@
         <v>1110</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
         <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>4170</v>
+        <v>8130</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>240</v>
+        <v>690</v>
       </c>
       <c r="O5" t="n">
-        <v>960</v>
+        <v>1920</v>
       </c>
       <c r="P5" t="n">
-        <v>5220</v>
+        <v>9360</v>
       </c>
       <c r="Q5" t="n">
-        <v>447.95</v>
+        <v>2357.64</v>
       </c>
     </row>
     <row r="6">
@@ -5846,7 +5846,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>420</v>
+        <v>1200</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -5858,10 +5858,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>4110</v>
+        <v>9060</v>
       </c>
       <c r="Q6" t="n">
-        <v>33.45</v>
+        <v>176.04</v>
       </c>
     </row>
     <row r="7">
@@ -5899,7 +5899,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>90</v>
+        <v>390</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -5911,10 +5911,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1230</v>
+        <v>3000</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.72</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="8">
@@ -5952,7 +5952,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -5964,7 +5964,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>420</v>
+        <v>990</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -7073,7 +7073,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -7085,22 +7085,22 @@
         <v>0.66</v>
       </c>
       <c r="L5" t="n">
-        <v>875.7</v>
+        <v>1707.3</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.4</v>
+        <v>6.9</v>
       </c>
       <c r="O5" t="n">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="P5" t="n">
-        <v>104.4</v>
+        <v>187.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>22.4</v>
+        <v>117.88</v>
       </c>
     </row>
     <row r="6">
@@ -7138,7 +7138,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>155.4</v>
+        <v>444</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>616.5</v>
+        <v>1359</v>
       </c>
       <c r="Q6" t="n">
-        <v>25.09</v>
+        <v>132.03</v>
       </c>
     </row>
     <row r="7">
@@ -7191,7 +7191,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>54</v>
+        <v>234</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -7203,10 +7203,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>307.5</v>
+        <v>750</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.78</v>
+        <v>19.87</v>
       </c>
     </row>
     <row r="8">
@@ -7244,7 +7244,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>63.9</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -7256,7 +7256,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>159.6</v>
+        <v>376.2</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -8365,7 +8365,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>307800</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -8377,22 +8377,22 @@
         <v>32144.07</v>
       </c>
       <c r="L5" t="n">
-        <v>157626</v>
+        <v>307314</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>408</v>
+        <v>1173</v>
       </c>
       <c r="O5" t="n">
-        <v>8160</v>
+        <v>16320</v>
       </c>
       <c r="P5" t="n">
-        <v>6786</v>
+        <v>12168</v>
       </c>
       <c r="Q5" t="n">
-        <v>13438.55</v>
+        <v>70729.2</v>
       </c>
     </row>
     <row r="6">
@@ -8430,7 +8430,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>27972</v>
+        <v>79920</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -8442,10 +8442,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>40072.5</v>
+        <v>88335</v>
       </c>
       <c r="Q6" t="n">
-        <v>15051.42</v>
+        <v>79218</v>
       </c>
     </row>
     <row r="7">
@@ -8483,7 +8483,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>9720</v>
+        <v>42120</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -8495,10 +8495,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>19987.5</v>
+        <v>48750</v>
       </c>
       <c r="Q7" t="n">
-        <v>2265.41</v>
+        <v>11923.2</v>
       </c>
     </row>
     <row r="8">
@@ -8536,7 +8536,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>11502</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -8548,7 +8548,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>10374</v>
+        <v>24453</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -9604,7 +9604,7 @@
         <v>11100</v>
       </c>
       <c r="H4" t="n">
-        <v>1770</v>
+        <v>1620</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -9616,22 +9616,22 @@
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>10860</v>
+        <v>16950</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>9780</v>
+        <v>15120</v>
       </c>
       <c r="O4" t="n">
-        <v>31080</v>
+        <v>29400</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>5379.49</v>
+        <v>29191.05</v>
       </c>
     </row>
     <row r="5">
@@ -9657,7 +9657,7 @@
         <v>2340</v>
       </c>
       <c r="H5" t="n">
-        <v>330</v>
+        <v>870</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -9669,22 +9669,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1500</v>
+        <v>3030</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="O5" t="n">
-        <v>29940</v>
+        <v>32280</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>793.54</v>
+        <v>4306.05</v>
       </c>
     </row>
     <row r="6">
@@ -9722,7 +9722,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -9731,13 +9731,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>8040</v>
+        <v>12420</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>129.57</v>
+        <v>703.08</v>
       </c>
     </row>
     <row r="7">
@@ -9784,13 +9784,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1080</v>
+        <v>1560</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>13.12</v>
+        <v>71.19</v>
       </c>
     </row>
     <row r="8">
@@ -9837,13 +9837,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>600</v>
+        <v>870</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.6</v>
+        <v>19.53</v>
       </c>
     </row>
     <row r="9">
@@ -9890,7 +9890,7 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -10949,7 +10949,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>118.8</v>
+        <v>313.2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -10961,22 +10961,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>315</v>
+        <v>636.3</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="O5" t="n">
-        <v>1497</v>
+        <v>1614</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>39.68</v>
+        <v>215.3</v>
       </c>
     </row>
     <row r="6">
@@ -11014,7 +11014,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>77.7</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -11023,13 +11023,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2010</v>
+        <v>3105</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>97.18000000000001</v>
+        <v>527.3099999999999</v>
       </c>
     </row>
     <row r="7">
@@ -11076,13 +11076,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>378</v>
+        <v>546</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>10.5</v>
+        <v>56.95</v>
       </c>
     </row>
     <row r="8">
@@ -11129,13 +11129,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>270</v>
+        <v>391.5</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.42</v>
+        <v>18.55</v>
       </c>
     </row>
     <row r="9">
@@ -11182,7 +11182,7 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>16.5</v>
+        <v>49.5</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -12241,7 +12241,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>677160</v>
+        <v>1785240</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -12253,22 +12253,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>56700</v>
+        <v>114534</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1632</v>
       </c>
       <c r="O5" t="n">
-        <v>254490</v>
+        <v>274380</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>23806.31</v>
+        <v>129181.5</v>
       </c>
     </row>
     <row r="6">
@@ -12306,7 +12306,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>13986</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -12315,13 +12315,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>341700</v>
+        <v>527850</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>58305.42</v>
+        <v>316386</v>
       </c>
     </row>
     <row r="7">
@@ -12368,13 +12368,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>64260</v>
+        <v>92820</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>6297.26</v>
+        <v>34171.2</v>
       </c>
     </row>
     <row r="8">
@@ -12421,13 +12421,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>45900</v>
+        <v>66555</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2051.49</v>
+        <v>11132.1</v>
       </c>
     </row>
     <row r="9">
@@ -12474,7 +12474,7 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2805</v>
+        <v>8415</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -13480,7 +13480,7 @@
         <v>60390</v>
       </c>
       <c r="H4" t="n">
-        <v>10200</v>
+        <v>12540</v>
       </c>
       <c r="I4" t="n">
         <v>3</v>
@@ -13492,19 +13492,19 @@
         <v>72</v>
       </c>
       <c r="L4" t="n">
-        <v>164370</v>
+        <v>181590</v>
       </c>
       <c r="M4" t="n">
-        <v>10080</v>
+        <v>11340</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>57000</v>
+        <v>76140</v>
       </c>
       <c r="P4" t="n">
-        <v>46770</v>
+        <v>36390</v>
       </c>
       <c r="Q4" t="n">
         <v>30362.45</v>
@@ -13533,7 +13533,7 @@
         <v>14130</v>
       </c>
       <c r="H5" t="n">
-        <v>1170</v>
+        <v>1770</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -13545,19 +13545,19 @@
         <v>6</v>
       </c>
       <c r="L5" t="n">
-        <v>54660</v>
+        <v>62610</v>
       </c>
       <c r="M5" t="n">
-        <v>3810</v>
+        <v>11850</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>16440</v>
+        <v>21690</v>
       </c>
       <c r="P5" t="n">
-        <v>46020</v>
+        <v>50670</v>
       </c>
       <c r="Q5" t="n">
         <v>6048.16</v>
@@ -13586,7 +13586,7 @@
         <v>1440</v>
       </c>
       <c r="H6" t="n">
-        <v>60</v>
+        <v>270</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -13598,19 +13598,19 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>15180</v>
+        <v>24840</v>
       </c>
       <c r="M6" t="n">
-        <v>1800</v>
+        <v>13590</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>12180</v>
+        <v>11880</v>
       </c>
       <c r="P6" t="n">
-        <v>42720</v>
+        <v>49830</v>
       </c>
       <c r="Q6" t="n">
         <v>1786.16</v>
@@ -13651,19 +13651,19 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>6840</v>
+        <v>21600</v>
       </c>
       <c r="M7" t="n">
-        <v>480</v>
+        <v>9690</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3060</v>
+        <v>6090</v>
       </c>
       <c r="P7" t="n">
-        <v>40590</v>
+        <v>55380</v>
       </c>
       <c r="Q7" t="n">
         <v>253.22</v>
@@ -13704,19 +13704,19 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3120</v>
+        <v>24870</v>
       </c>
       <c r="M8" t="n">
-        <v>180</v>
+        <v>7650</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P8" t="n">
-        <v>32490</v>
+        <v>54660</v>
       </c>
       <c r="Q8" t="n">
         <v>117.4</v>
@@ -13757,19 +13757,19 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2310</v>
+        <v>24240</v>
       </c>
       <c r="M9" t="n">
-        <v>90</v>
+        <v>4110</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P9" t="n">
-        <v>24990</v>
+        <v>45330</v>
       </c>
       <c r="Q9" t="n">
         <v>82.25</v>
@@ -13798,7 +13798,7 @@
         <v>30</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -13810,10 +13810,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>960</v>
+        <v>18330</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>870</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -13822,7 +13822,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>18180</v>
+        <v>35430</v>
       </c>
       <c r="Q10" t="n">
         <v>32.48</v>
@@ -13863,10 +13863,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>180</v>
+        <v>4230</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -13875,7 +13875,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>9780</v>
+        <v>25530</v>
       </c>
       <c r="Q11" t="n">
         <v>9.710000000000001</v>
@@ -13916,7 +13916,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2220</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -13928,7 +13928,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3480</v>
+        <v>7650</v>
       </c>
       <c r="Q12" t="n">
         <v>4.24</v>
@@ -13969,7 +13969,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>30</v>
+        <v>750</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -13981,7 +13981,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>540</v>
+        <v>1290</v>
       </c>
       <c r="Q13" t="n">
         <v>0.89</v>
@@ -14825,7 +14825,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2224.8</v>
+        <v>3261.6</v>
       </c>
       <c r="I5" t="n">
         <v>0.66</v>
@@ -14837,22 +14837,22 @@
         <v>9.93</v>
       </c>
       <c r="L5" t="n">
-        <v>48176.1</v>
+        <v>63189</v>
       </c>
       <c r="M5" t="n">
-        <v>361.2</v>
+        <v>929.4</v>
       </c>
       <c r="N5" t="n">
-        <v>69.59999999999999</v>
+        <v>118.5</v>
       </c>
       <c r="O5" t="n">
-        <v>4228.5</v>
+        <v>5583</v>
       </c>
       <c r="P5" t="n">
-        <v>2061</v>
+        <v>2082.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>2011.02</v>
+        <v>20840.01</v>
       </c>
     </row>
     <row r="6">
@@ -14878,7 +14878,7 @@
         <v>1582.5</v>
       </c>
       <c r="H6" t="n">
-        <v>2171.7</v>
+        <v>2530.8</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -14890,22 +14890,22 @@
         <v>1.01</v>
       </c>
       <c r="L6" t="n">
-        <v>29736.9</v>
+        <v>42157.8</v>
       </c>
       <c r="M6" t="n">
-        <v>549.6</v>
+        <v>2652</v>
       </c>
       <c r="N6" t="n">
-        <v>48</v>
+        <v>148.5</v>
       </c>
       <c r="O6" t="n">
-        <v>8265</v>
+        <v>11842.5</v>
       </c>
       <c r="P6" t="n">
-        <v>14715</v>
+        <v>16735.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>16812.15</v>
+        <v>174222.68</v>
       </c>
     </row>
     <row r="7">
@@ -14931,7 +14931,7 @@
         <v>2484</v>
       </c>
       <c r="H7" t="n">
-        <v>175.2</v>
+        <v>591.3</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -14943,22 +14943,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>25398</v>
+        <v>46638</v>
       </c>
       <c r="M7" t="n">
-        <v>1365</v>
+        <v>7801.5</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2142</v>
+        <v>5239.5</v>
       </c>
       <c r="P7" t="n">
-        <v>21277.5</v>
+        <v>27262.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>11632.74</v>
+        <v>120548.93</v>
       </c>
     </row>
     <row r="8">
@@ -14984,7 +14984,7 @@
         <v>8151</v>
       </c>
       <c r="H8" t="n">
-        <v>102</v>
+        <v>382.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -14996,22 +14996,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>12141</v>
+        <v>34058.7</v>
       </c>
       <c r="M8" t="n">
-        <v>676.5</v>
+        <v>9454.5</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>364.5</v>
+        <v>972</v>
       </c>
       <c r="P8" t="n">
-        <v>23757.6</v>
+        <v>39352.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>8294.049999999999</v>
+        <v>85950.44</v>
       </c>
     </row>
     <row r="9">
@@ -15037,7 +15037,7 @@
         <v>2116.5</v>
       </c>
       <c r="H9" t="n">
-        <v>90</v>
+        <v>210</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -15049,22 +15049,22 @@
         <v>1.61</v>
       </c>
       <c r="L9" t="n">
-        <v>4787.1</v>
+        <v>27945</v>
       </c>
       <c r="M9" t="n">
-        <v>273</v>
+        <v>5859</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>16.5</v>
+        <v>66</v>
       </c>
       <c r="P9" t="n">
-        <v>23415</v>
+        <v>40170</v>
       </c>
       <c r="Q9" t="n">
-        <v>4462.26</v>
+        <v>46241.92</v>
       </c>
     </row>
     <row r="10">
@@ -15090,7 +15090,7 @@
         <v>810</v>
       </c>
       <c r="H10" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -15102,10 +15102,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2563.2</v>
+        <v>21279.9</v>
       </c>
       <c r="M10" t="n">
-        <v>204</v>
+        <v>2524.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -15114,10 +15114,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>30447</v>
+        <v>54366</v>
       </c>
       <c r="Q10" t="n">
-        <v>2356.55</v>
+        <v>24420.65</v>
       </c>
     </row>
     <row r="11">
@@ -15155,10 +15155,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1650</v>
+        <v>7170</v>
       </c>
       <c r="M11" t="n">
-        <v>27</v>
+        <v>2889</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -15167,10 +15167,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>17388</v>
+        <v>38286</v>
       </c>
       <c r="Q11" t="n">
-        <v>1392.77</v>
+        <v>14433.12</v>
       </c>
     </row>
     <row r="12">
@@ -15208,10 +15208,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>330</v>
+        <v>3990</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3448.5</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -15220,10 +15220,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>14490</v>
+        <v>28560</v>
       </c>
       <c r="Q12" t="n">
-        <v>1065.33</v>
+        <v>11039.95</v>
       </c>
     </row>
     <row r="13">
@@ -15249,7 +15249,7 @@
         <v>150</v>
       </c>
       <c r="H13" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -15261,10 +15261,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>270</v>
+        <v>1290</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>660</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -15273,10 +15273,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2730</v>
+        <v>6480</v>
       </c>
       <c r="Q13" t="n">
-        <v>1049.93</v>
+        <v>10880.35</v>
       </c>
     </row>
     <row r="14">
@@ -15314,22 +15314,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
+        <v>1410</v>
+      </c>
+      <c r="M14" t="n">
+        <v>150</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
         <v>540</v>
       </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>240</v>
-      </c>
       <c r="Q14" t="n">
-        <v>1087.21</v>
+        <v>11266.62</v>
       </c>
     </row>
     <row r="15">
@@ -15367,10 +15367,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -15382,7 +15382,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>466.04</v>
+        <v>4829.54</v>
       </c>
     </row>
     <row r="16">
@@ -15420,7 +15420,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -15435,7 +15435,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>173.43</v>
+        <v>1797.2</v>
       </c>
     </row>
     <row r="17">
@@ -15473,7 +15473,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -15488,7 +15488,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>37.83</v>
+        <v>392.05</v>
       </c>
     </row>
     <row r="18">
@@ -15526,7 +15526,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -15541,7 +15541,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.68</v>
+        <v>38.16</v>
       </c>
     </row>
     <row r="19">
@@ -15594,7 +15594,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.22</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="20">
@@ -16117,7 +16117,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>421.2</v>
+        <v>637.2</v>
       </c>
       <c r="I5" t="n">
         <v>0.33</v>
@@ -16129,19 +16129,19 @@
         <v>1.99</v>
       </c>
       <c r="L5" t="n">
-        <v>11478.6</v>
+        <v>13148.1</v>
       </c>
       <c r="M5" t="n">
-        <v>76.2</v>
+        <v>237</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>822</v>
+        <v>1084.5</v>
       </c>
       <c r="P5" t="n">
-        <v>920.4</v>
+        <v>1013.4</v>
       </c>
       <c r="Q5" t="n">
         <v>302.41</v>
@@ -16170,7 +16170,7 @@
         <v>72</v>
       </c>
       <c r="H6" t="n">
-        <v>34.2</v>
+        <v>153.9</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -16182,19 +16182,19 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>5616.6</v>
+        <v>9190.799999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>144</v>
+        <v>1087.2</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3045</v>
+        <v>2970</v>
       </c>
       <c r="P6" t="n">
-        <v>6408</v>
+        <v>7474.5</v>
       </c>
       <c r="Q6" t="n">
         <v>1339.62</v>
@@ -16235,19 +16235,19 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>4104</v>
+        <v>12960</v>
       </c>
       <c r="M7" t="n">
-        <v>168</v>
+        <v>3391.5</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1071</v>
+        <v>2131.5</v>
       </c>
       <c r="P7" t="n">
-        <v>10147.5</v>
+        <v>13845</v>
       </c>
       <c r="Q7" t="n">
         <v>202.58</v>
@@ -16288,19 +16288,19 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2215.2</v>
+        <v>17657.7</v>
       </c>
       <c r="M8" t="n">
-        <v>99</v>
+        <v>4207.5</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="P8" t="n">
-        <v>12346.2</v>
+        <v>20770.8</v>
       </c>
       <c r="Q8" t="n">
         <v>111.53</v>
@@ -16341,19 +16341,19 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1871.1</v>
+        <v>19634.4</v>
       </c>
       <c r="M9" t="n">
-        <v>63</v>
+        <v>2877</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="P9" t="n">
-        <v>12495</v>
+        <v>22665</v>
       </c>
       <c r="Q9" t="n">
         <v>79.78</v>
@@ -16382,7 +16382,7 @@
         <v>30</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -16394,10 +16394,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>854.4</v>
+        <v>16313.7</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>739.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -16406,7 +16406,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>15453</v>
+        <v>30115.5</v>
       </c>
       <c r="Q10" t="n">
         <v>32.48</v>
@@ -16447,10 +16447,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>180</v>
+        <v>4230</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -16459,7 +16459,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>8802</v>
+        <v>22977</v>
       </c>
       <c r="Q11" t="n">
         <v>9.710000000000001</v>
@@ -16500,7 +16500,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2220</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -16512,7 +16512,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3480</v>
+        <v>7650</v>
       </c>
       <c r="Q12" t="n">
         <v>4.24</v>
@@ -16553,7 +16553,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>30</v>
+        <v>750</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -16565,7 +16565,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>540</v>
+        <v>1290</v>
       </c>
       <c r="Q13" t="n">
         <v>0.89</v>
@@ -17409,7 +17409,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2400840</v>
+        <v>3632040</v>
       </c>
       <c r="I5" t="n">
         <v>64288.14</v>
@@ -17421,19 +17421,19 @@
         <v>96432.22</v>
       </c>
       <c r="L5" t="n">
-        <v>2066148</v>
+        <v>2366658</v>
       </c>
       <c r="M5" t="n">
-        <v>26670</v>
+        <v>82950</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>139740</v>
+        <v>184365</v>
       </c>
       <c r="P5" t="n">
-        <v>59826</v>
+        <v>65871</v>
       </c>
       <c r="Q5" t="n">
         <v>181444.86</v>
@@ -17462,7 +17462,7 @@
         <v>3888</v>
       </c>
       <c r="H6" t="n">
-        <v>194940</v>
+        <v>877230</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -17474,19 +17474,19 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1010988</v>
+        <v>1654344</v>
       </c>
       <c r="M6" t="n">
-        <v>50400</v>
+        <v>380520</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>517650</v>
+        <v>504900</v>
       </c>
       <c r="P6" t="n">
-        <v>416520</v>
+        <v>485842.5</v>
       </c>
       <c r="Q6" t="n">
         <v>803771.1</v>
@@ -17527,19 +17527,19 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>738720</v>
+        <v>2332800</v>
       </c>
       <c r="M7" t="n">
-        <v>58800</v>
+        <v>1187025</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>182070</v>
+        <v>362355</v>
       </c>
       <c r="P7" t="n">
-        <v>659587.5</v>
+        <v>899925</v>
       </c>
       <c r="Q7" t="n">
         <v>121545.79</v>
@@ -17580,19 +17580,19 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>398736</v>
+        <v>3178386</v>
       </c>
       <c r="M8" t="n">
-        <v>34650</v>
+        <v>1472625</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2295</v>
       </c>
       <c r="P8" t="n">
-        <v>802503</v>
+        <v>1350102</v>
       </c>
       <c r="Q8" t="n">
         <v>66919.82000000001</v>
@@ -17633,19 +17633,19 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>336798</v>
+        <v>3534192</v>
       </c>
       <c r="M9" t="n">
-        <v>22050</v>
+        <v>1006950</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2805</v>
       </c>
       <c r="P9" t="n">
-        <v>812175</v>
+        <v>1473225</v>
       </c>
       <c r="Q9" t="n">
         <v>47869.03</v>
@@ -17674,7 +17674,7 @@
         <v>1620</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>513000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -17686,10 +17686,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>153792</v>
+        <v>2936466</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>258825</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -17698,7 +17698,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1004445</v>
+        <v>1957507.5</v>
       </c>
       <c r="Q10" t="n">
         <v>19485.36</v>
@@ -17739,10 +17739,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>32400</v>
+        <v>761400</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>18900</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -17751,7 +17751,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>572130</v>
+        <v>1493505</v>
       </c>
       <c r="Q11" t="n">
         <v>5825.52</v>
@@ -17792,7 +17792,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>399600</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -17804,7 +17804,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>226200</v>
+        <v>497250</v>
       </c>
       <c r="Q12" t="n">
         <v>2544.48</v>
@@ -17845,7 +17845,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>5400</v>
+        <v>135000</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -17857,7 +17857,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>35100</v>
+        <v>83850</v>
       </c>
       <c r="Q13" t="n">
         <v>535.6799999999999</v>
@@ -18648,7 +18648,7 @@
         <v>19830</v>
       </c>
       <c r="H4" t="n">
-        <v>2100</v>
+        <v>2940</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -18660,22 +18660,22 @@
         <v>16</v>
       </c>
       <c r="L4" t="n">
-        <v>89490</v>
+        <v>118110</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>540</v>
+        <v>870</v>
       </c>
       <c r="O4" t="n">
-        <v>35790</v>
+        <v>49200</v>
       </c>
       <c r="P4" t="n">
-        <v>3450</v>
+        <v>4650</v>
       </c>
       <c r="Q4" t="n">
-        <v>6499.7</v>
+        <v>74475.72</v>
       </c>
     </row>
     <row r="5">
@@ -18701,7 +18701,7 @@
         <v>1950</v>
       </c>
       <c r="H5" t="n">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -18713,22 +18713,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>13710</v>
+        <v>21270</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="O5" t="n">
-        <v>5910</v>
+        <v>9360</v>
       </c>
       <c r="P5" t="n">
-        <v>1170</v>
+        <v>4380</v>
       </c>
       <c r="Q5" t="n">
-        <v>565.66</v>
+        <v>6481.53</v>
       </c>
     </row>
     <row r="6">
@@ -18766,7 +18766,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>720</v>
+        <v>1680</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -18775,13 +18775,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>420</v>
+        <v>900</v>
       </c>
       <c r="P6" t="n">
-        <v>570</v>
+        <v>2280</v>
       </c>
       <c r="Q6" t="n">
-        <v>64.2</v>
+        <v>735.5700000000001</v>
       </c>
     </row>
     <row r="7">
@@ -18831,10 +18831,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>330</v>
+        <v>1770</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.33</v>
+        <v>26.73</v>
       </c>
     </row>
     <row r="8">
@@ -18872,7 +18872,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>150</v>
+        <v>330</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -18884,10 +18884,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.17</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="9">
@@ -19993,7 +19993,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>32.4</v>
+        <v>97.2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -20005,22 +20005,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>2879.1</v>
+        <v>4466.7</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O5" t="n">
-        <v>295.5</v>
+        <v>468</v>
       </c>
       <c r="P5" t="n">
-        <v>23.4</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>28.28</v>
+        <v>324.08</v>
       </c>
     </row>
     <row r="6">
@@ -20058,7 +20058,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>266.4</v>
+        <v>621.6</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -20067,13 +20067,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>105</v>
+        <v>225</v>
       </c>
       <c r="P6" t="n">
-        <v>85.5</v>
+        <v>342</v>
       </c>
       <c r="Q6" t="n">
-        <v>48.15</v>
+        <v>551.6799999999999</v>
       </c>
     </row>
     <row r="7">
@@ -20123,10 +20123,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>82.5</v>
+        <v>442.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.87</v>
+        <v>21.38</v>
       </c>
     </row>
     <row r="8">
@@ -20164,7 +20164,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>106.5</v>
+        <v>234.3</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -20176,10 +20176,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>11.4</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.16</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="9">
@@ -21285,7 +21285,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>184680</v>
+        <v>554040</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -21297,22 +21297,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>518238</v>
+        <v>804006</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>357</v>
       </c>
       <c r="O5" t="n">
-        <v>50235</v>
+        <v>79560</v>
       </c>
       <c r="P5" t="n">
-        <v>1521</v>
+        <v>5694</v>
       </c>
       <c r="Q5" t="n">
-        <v>16969.82</v>
+        <v>194445.9</v>
       </c>
     </row>
     <row r="6">
@@ -21350,7 +21350,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>47952</v>
+        <v>111888</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -21359,13 +21359,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>17850</v>
+        <v>38250</v>
       </c>
       <c r="P6" t="n">
-        <v>5557.5</v>
+        <v>22230</v>
       </c>
       <c r="Q6" t="n">
-        <v>28887.84</v>
+        <v>331006.5</v>
       </c>
     </row>
     <row r="7">
@@ -21415,10 +21415,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>5362.5</v>
+        <v>28762.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>1119.74</v>
+        <v>12830.4</v>
       </c>
     </row>
     <row r="8">
@@ -21456,7 +21456,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>19170</v>
+        <v>42174</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -21468,10 +21468,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>741</v>
+        <v>4446</v>
       </c>
       <c r="Q8" t="n">
-        <v>98.5</v>
+        <v>1128.6</v>
       </c>
     </row>
     <row r="9">
@@ -22577,7 +22577,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>12681360</v>
+        <v>18591120</v>
       </c>
       <c r="I5" t="n">
         <v>128576.29</v>
@@ -22589,22 +22589,22 @@
         <v>482161.08</v>
       </c>
       <c r="L5" t="n">
-        <v>8671698</v>
+        <v>11374020</v>
       </c>
       <c r="M5" t="n">
-        <v>126420</v>
+        <v>325290</v>
       </c>
       <c r="N5" t="n">
-        <v>11832</v>
+        <v>20145</v>
       </c>
       <c r="O5" t="n">
-        <v>718845</v>
+        <v>949110</v>
       </c>
       <c r="P5" t="n">
-        <v>133965</v>
+        <v>135369</v>
       </c>
       <c r="Q5" t="n">
-        <v>1206612.5</v>
+        <v>12504008.61</v>
       </c>
     </row>
     <row r="6">
@@ -22630,7 +22630,7 @@
         <v>85455</v>
       </c>
       <c r="H6" t="n">
-        <v>12378690</v>
+        <v>14425560</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -22642,22 +22642,22 @@
         <v>49235.78</v>
       </c>
       <c r="L6" t="n">
-        <v>5352642</v>
+        <v>7588404</v>
       </c>
       <c r="M6" t="n">
-        <v>192360</v>
+        <v>928200</v>
       </c>
       <c r="N6" t="n">
-        <v>8160</v>
+        <v>25245</v>
       </c>
       <c r="O6" t="n">
-        <v>1405050</v>
+        <v>2013225</v>
       </c>
       <c r="P6" t="n">
-        <v>956475</v>
+        <v>1087807.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>10087289.64</v>
+        <v>104533606.35</v>
       </c>
     </row>
     <row r="7">
@@ -22683,7 +22683,7 @@
         <v>134136</v>
       </c>
       <c r="H7" t="n">
-        <v>998640</v>
+        <v>3370410</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -22695,22 +22695,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>4571640</v>
+        <v>8394840</v>
       </c>
       <c r="M7" t="n">
-        <v>477750</v>
+        <v>2730525</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>364140</v>
+        <v>890715</v>
       </c>
       <c r="P7" t="n">
-        <v>1383037.5</v>
+        <v>1772062.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>6979642.56</v>
+        <v>72329360.40000001</v>
       </c>
     </row>
     <row r="8">
@@ -22736,7 +22736,7 @@
         <v>440154</v>
       </c>
       <c r="H8" t="n">
-        <v>581400</v>
+        <v>2180250</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -22748,22 +22748,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2185380</v>
+        <v>6130566</v>
       </c>
       <c r="M8" t="n">
-        <v>236775</v>
+        <v>3309075</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>61965</v>
+        <v>165240</v>
       </c>
       <c r="P8" t="n">
-        <v>1544244</v>
+        <v>2557932</v>
       </c>
       <c r="Q8" t="n">
-        <v>4976430.37</v>
+        <v>51570266.35</v>
       </c>
     </row>
     <row r="9">
@@ -22789,7 +22789,7 @@
         <v>114291</v>
       </c>
       <c r="H9" t="n">
-        <v>513000</v>
+        <v>1197000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -22801,22 +22801,22 @@
         <v>77980.94</v>
       </c>
       <c r="L9" t="n">
-        <v>861678</v>
+        <v>5030100</v>
       </c>
       <c r="M9" t="n">
-        <v>95550</v>
+        <v>2050650</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2805</v>
+        <v>11220</v>
       </c>
       <c r="P9" t="n">
-        <v>1521975</v>
+        <v>2611050</v>
       </c>
       <c r="Q9" t="n">
-        <v>2677353.42</v>
+        <v>27745154.34</v>
       </c>
     </row>
     <row r="10">
@@ -22842,7 +22842,7 @@
         <v>43740</v>
       </c>
       <c r="H10" t="n">
-        <v>171000</v>
+        <v>1026000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -22854,10 +22854,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>461376</v>
+        <v>3830382</v>
       </c>
       <c r="M10" t="n">
-        <v>71400</v>
+        <v>883575</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -22866,10 +22866,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1979055</v>
+        <v>3533790</v>
       </c>
       <c r="Q10" t="n">
-        <v>1413927.36</v>
+        <v>14652392.4</v>
       </c>
     </row>
     <row r="11">
@@ -22907,10 +22907,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>297000</v>
+        <v>1290600</v>
       </c>
       <c r="M11" t="n">
-        <v>9450</v>
+        <v>1011150</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -22919,10 +22919,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1130220</v>
+        <v>2488590</v>
       </c>
       <c r="Q11" t="n">
-        <v>835660.8</v>
+        <v>8659872</v>
       </c>
     </row>
     <row r="12">
@@ -22960,10 +22960,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>59400</v>
+        <v>718200</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1206975</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -22972,10 +22972,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>941850</v>
+        <v>1856400</v>
       </c>
       <c r="Q12" t="n">
-        <v>639200.16</v>
+        <v>6623969.4</v>
       </c>
     </row>
     <row r="13">
@@ -23001,7 +23001,7 @@
         <v>8100</v>
       </c>
       <c r="H13" t="n">
-        <v>171000</v>
+        <v>513000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -23013,10 +23013,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>48600</v>
+        <v>232200</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>231000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -23025,10 +23025,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>177450</v>
+        <v>421200</v>
       </c>
       <c r="Q13" t="n">
-        <v>629959.6800000001</v>
+        <v>6528211.2</v>
       </c>
     </row>
     <row r="14">
@@ -23066,10 +23066,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>97200</v>
+        <v>253800</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>52500</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -23078,10 +23078,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>15600</v>
+        <v>35100</v>
       </c>
       <c r="Q14" t="n">
-        <v>652324.3199999999</v>
+        <v>6759973.8</v>
       </c>
     </row>
     <row r="15">
@@ -23119,10 +23119,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>172800</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>84000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -23134,7 +23134,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>279624.96</v>
+        <v>2897726.4</v>
       </c>
     </row>
     <row r="16">
@@ -23172,7 +23172,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>64800</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -23187,7 +23187,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>104055.84</v>
+        <v>1078320.6</v>
       </c>
     </row>
     <row r="17">
@@ -23225,7 +23225,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -23240,7 +23240,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>22699.44</v>
+        <v>235232.1</v>
       </c>
     </row>
     <row r="18">
@@ -23278,7 +23278,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -23293,7 +23293,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2209.68</v>
+        <v>22898.7</v>
       </c>
     </row>
     <row r="19">
@@ -23346,7 +23346,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>133.92</v>
+        <v>1387.8</v>
       </c>
     </row>
     <row r="20">
@@ -23816,7 +23816,7 @@
         <v>69750</v>
       </c>
       <c r="H4" t="n">
-        <v>3180</v>
+        <v>5040</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -23828,22 +23828,22 @@
         <v>28</v>
       </c>
       <c r="L4" t="n">
-        <v>150180</v>
+        <v>212100</v>
       </c>
       <c r="M4" t="n">
-        <v>15690</v>
+        <v>44640</v>
       </c>
       <c r="N4" t="n">
-        <v>9300</v>
+        <v>13230</v>
       </c>
       <c r="O4" t="n">
-        <v>17280</v>
+        <v>39240</v>
       </c>
       <c r="P4" t="n">
-        <v>26040</v>
+        <v>22710</v>
       </c>
       <c r="Q4" t="n">
-        <v>23161.51</v>
+        <v>227073.6</v>
       </c>
     </row>
     <row r="5">
@@ -23869,7 +23869,7 @@
         <v>28710</v>
       </c>
       <c r="H5" t="n">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -23881,22 +23881,22 @@
         <v>6</v>
       </c>
       <c r="L5" t="n">
-        <v>49740</v>
+        <v>78780</v>
       </c>
       <c r="M5" t="n">
-        <v>2550</v>
+        <v>16860</v>
       </c>
       <c r="N5" t="n">
-        <v>2310</v>
+        <v>2880</v>
       </c>
       <c r="O5" t="n">
-        <v>3480</v>
+        <v>5910</v>
       </c>
       <c r="P5" t="n">
-        <v>29190</v>
+        <v>34890</v>
       </c>
       <c r="Q5" t="n">
-        <v>10437.57</v>
+        <v>102329.1</v>
       </c>
     </row>
     <row r="6">
@@ -23934,22 +23934,22 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>19620</v>
+        <v>32370</v>
       </c>
       <c r="M6" t="n">
-        <v>30</v>
+        <v>5460</v>
       </c>
       <c r="N6" t="n">
-        <v>540</v>
+        <v>990</v>
       </c>
       <c r="O6" t="n">
-        <v>270</v>
+        <v>2040</v>
       </c>
       <c r="P6" t="n">
-        <v>26640</v>
+        <v>37080</v>
       </c>
       <c r="Q6" t="n">
-        <v>4922.5</v>
+        <v>48259.8</v>
       </c>
     </row>
     <row r="7">
@@ -23987,22 +23987,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>7890</v>
+        <v>17880</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2940</v>
       </c>
       <c r="P7" t="n">
-        <v>19470</v>
+        <v>29970</v>
       </c>
       <c r="Q7" t="n">
-        <v>2302.25</v>
+        <v>22571.1</v>
       </c>
     </row>
     <row r="8">
@@ -24040,10 +24040,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2250</v>
+        <v>4440</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1440</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -24052,10 +24052,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>6330</v>
+        <v>8310</v>
       </c>
       <c r="Q8" t="n">
-        <v>967.2</v>
+        <v>9482.4</v>
       </c>
     </row>
     <row r="9">
@@ -24093,10 +24093,10 @@
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>810</v>
+        <v>1620</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -24105,10 +24105,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>6060</v>
+        <v>4170</v>
       </c>
       <c r="Q9" t="n">
-        <v>368.03</v>
+        <v>3608.1</v>
       </c>
     </row>
     <row r="10">
@@ -24146,10 +24146,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>300</v>
+        <v>390</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -24158,10 +24158,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>10200</v>
+        <v>15660</v>
       </c>
       <c r="Q10" t="n">
-        <v>173.96</v>
+        <v>1705.5</v>
       </c>
     </row>
     <row r="11">
@@ -24199,7 +24199,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -24211,10 +24211,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3930</v>
+        <v>6930</v>
       </c>
       <c r="Q11" t="n">
-        <v>79.41</v>
+        <v>778.5</v>
       </c>
     </row>
     <row r="12">
@@ -24252,7 +24252,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -24264,10 +24264,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>5310</v>
+        <v>8790</v>
       </c>
       <c r="Q12" t="n">
-        <v>60.13</v>
+        <v>589.5</v>
       </c>
     </row>
     <row r="13">
@@ -24317,10 +24317,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>210</v>
+        <v>1980</v>
       </c>
       <c r="Q13" t="n">
-        <v>25.7</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14">
@@ -24373,7 +24373,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>23.5</v>
+        <v>230.4</v>
       </c>
     </row>
     <row r="15">
@@ -25161,7 +25161,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>64.8</v>
+        <v>108</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -25173,22 +25173,22 @@
         <v>1.99</v>
       </c>
       <c r="L5" t="n">
-        <v>10445.4</v>
+        <v>16543.8</v>
       </c>
       <c r="M5" t="n">
-        <v>51</v>
+        <v>337.2</v>
       </c>
       <c r="N5" t="n">
-        <v>23.1</v>
+        <v>28.8</v>
       </c>
       <c r="O5" t="n">
-        <v>174</v>
+        <v>295.5</v>
       </c>
       <c r="P5" t="n">
-        <v>583.8</v>
+        <v>697.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>521.88</v>
+        <v>5116.46</v>
       </c>
     </row>
     <row r="6">
@@ -25226,22 +25226,22 @@
         <v>0.51</v>
       </c>
       <c r="L6" t="n">
-        <v>7259.4</v>
+        <v>11976.9</v>
       </c>
       <c r="M6" t="n">
-        <v>2.4</v>
+        <v>436.8</v>
       </c>
       <c r="N6" t="n">
-        <v>27</v>
+        <v>49.5</v>
       </c>
       <c r="O6" t="n">
-        <v>67.5</v>
+        <v>510</v>
       </c>
       <c r="P6" t="n">
-        <v>3996</v>
+        <v>5562</v>
       </c>
       <c r="Q6" t="n">
-        <v>3691.87</v>
+        <v>36194.85</v>
       </c>
     </row>
     <row r="7">
@@ -25279,22 +25279,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>4734</v>
+        <v>10728</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1050</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1029</v>
       </c>
       <c r="P7" t="n">
-        <v>4867.5</v>
+        <v>7492.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>1841.8</v>
+        <v>18056.88</v>
       </c>
     </row>
     <row r="8">
@@ -25332,10 +25332,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1597.5</v>
+        <v>3152.4</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -25344,10 +25344,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2405.4</v>
+        <v>3157.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>918.84</v>
+        <v>9008.280000000001</v>
       </c>
     </row>
     <row r="9">
@@ -25385,10 +25385,10 @@
         <v>0.8</v>
       </c>
       <c r="L9" t="n">
-        <v>656.1</v>
+        <v>1312.2</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -25397,10 +25397,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3030</v>
+        <v>2085</v>
       </c>
       <c r="Q9" t="n">
-        <v>356.99</v>
+        <v>3499.86</v>
       </c>
     </row>
     <row r="10">
@@ -25438,10 +25438,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>267</v>
+        <v>347.1</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>25.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -25450,10 +25450,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>8670</v>
+        <v>13311</v>
       </c>
       <c r="Q10" t="n">
-        <v>173.96</v>
+        <v>1705.5</v>
       </c>
     </row>
     <row r="11">
@@ -25491,7 +25491,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -25503,10 +25503,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3537</v>
+        <v>6237</v>
       </c>
       <c r="Q11" t="n">
-        <v>79.41</v>
+        <v>778.5</v>
       </c>
     </row>
     <row r="12">
@@ -25544,7 +25544,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -25556,10 +25556,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>5310</v>
+        <v>8790</v>
       </c>
       <c r="Q12" t="n">
-        <v>60.13</v>
+        <v>589.5</v>
       </c>
     </row>
     <row r="13">
@@ -25609,10 +25609,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>210</v>
+        <v>1980</v>
       </c>
       <c r="Q13" t="n">
-        <v>25.7</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14">
@@ -25665,7 +25665,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>23.5</v>
+        <v>230.4</v>
       </c>
     </row>
     <row r="15">
@@ -26453,7 +26453,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>369360</v>
+        <v>615600</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -26465,22 +26465,22 @@
         <v>96432.22</v>
       </c>
       <c r="L5" t="n">
-        <v>1880172</v>
+        <v>2977884</v>
       </c>
       <c r="M5" t="n">
-        <v>17850</v>
+        <v>118020</v>
       </c>
       <c r="N5" t="n">
-        <v>3927</v>
+        <v>4896</v>
       </c>
       <c r="O5" t="n">
-        <v>29580</v>
+        <v>50235</v>
       </c>
       <c r="P5" t="n">
-        <v>37947</v>
+        <v>45357</v>
       </c>
       <c r="Q5" t="n">
-        <v>313127.05</v>
+        <v>3069873</v>
       </c>
     </row>
     <row r="6">
@@ -26518,22 +26518,22 @@
         <v>24617.89</v>
       </c>
       <c r="L6" t="n">
-        <v>1306692</v>
+        <v>2155842</v>
       </c>
       <c r="M6" t="n">
-        <v>840</v>
+        <v>152880</v>
       </c>
       <c r="N6" t="n">
-        <v>4590</v>
+        <v>8415</v>
       </c>
       <c r="O6" t="n">
-        <v>11475</v>
+        <v>86700</v>
       </c>
       <c r="P6" t="n">
-        <v>259740</v>
+        <v>361530</v>
       </c>
       <c r="Q6" t="n">
-        <v>2215124.82</v>
+        <v>21716910</v>
       </c>
     </row>
     <row r="7">
@@ -26571,22 +26571,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>852120</v>
+        <v>1931040</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>367500</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>174930</v>
       </c>
       <c r="P7" t="n">
-        <v>316387.5</v>
+        <v>487012.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>1105081.06</v>
+        <v>10834128</v>
       </c>
     </row>
     <row r="8">
@@ -26624,10 +26624,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>287550</v>
+        <v>567432</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>277200</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -26636,10 +26636,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>156351</v>
+        <v>205257</v>
       </c>
       <c r="Q8" t="n">
-        <v>551306.74</v>
+        <v>5404968</v>
       </c>
     </row>
     <row r="9">
@@ -26677,10 +26677,10 @@
         <v>38990.47</v>
       </c>
       <c r="L9" t="n">
-        <v>118098</v>
+        <v>236196</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>73500</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -26689,10 +26689,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>196950</v>
+        <v>135525</v>
       </c>
       <c r="Q9" t="n">
-        <v>214191.25</v>
+        <v>2099914.2</v>
       </c>
     </row>
     <row r="10">
@@ -26730,10 +26730,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>48060</v>
+        <v>62478</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>8925</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -26742,10 +26742,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>563550</v>
+        <v>865215</v>
       </c>
       <c r="Q10" t="n">
-        <v>104376.6</v>
+        <v>1023300</v>
       </c>
     </row>
     <row r="11">
@@ -26783,7 +26783,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>5400</v>
+        <v>32400</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -26795,10 +26795,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>229905</v>
+        <v>405405</v>
       </c>
       <c r="Q11" t="n">
-        <v>47644.2</v>
+        <v>467100</v>
       </c>
     </row>
     <row r="12">
@@ -26836,7 +26836,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -26848,10 +26848,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>345150</v>
+        <v>571350</v>
       </c>
       <c r="Q12" t="n">
-        <v>36077.4</v>
+        <v>353700</v>
       </c>
     </row>
     <row r="13">
@@ -26901,10 +26901,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>13650</v>
+        <v>128700</v>
       </c>
       <c r="Q13" t="n">
-        <v>15422.4</v>
+        <v>151200</v>
       </c>
     </row>
     <row r="14">
@@ -26957,7 +26957,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>14100.48</v>
+        <v>138240</v>
       </c>
     </row>
     <row r="15">
@@ -27692,7 +27692,7 @@
         <v>59400</v>
       </c>
       <c r="H4" t="n">
-        <v>18000</v>
+        <v>20850</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -27704,7 +27704,7 @@
         <v>31</v>
       </c>
       <c r="L4" t="n">
-        <v>172260</v>
+        <v>220260</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -27713,13 +27713,13 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>75120</v>
+        <v>90750</v>
       </c>
       <c r="P4" t="n">
-        <v>2790</v>
+        <v>60</v>
       </c>
       <c r="Q4" t="n">
-        <v>15511.74</v>
+        <v>215986.32</v>
       </c>
     </row>
     <row r="5">
@@ -27745,7 +27745,7 @@
         <v>19950</v>
       </c>
       <c r="H5" t="n">
-        <v>1830</v>
+        <v>2910</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -27757,7 +27757,7 @@
         <v>9</v>
       </c>
       <c r="L5" t="n">
-        <v>42840</v>
+        <v>56130</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -27766,13 +27766,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>21570</v>
+        <v>34110</v>
       </c>
       <c r="P5" t="n">
-        <v>3780</v>
+        <v>570</v>
       </c>
       <c r="Q5" t="n">
-        <v>3925.86</v>
+        <v>54663.84</v>
       </c>
     </row>
     <row r="6">
@@ -27798,7 +27798,7 @@
         <v>930</v>
       </c>
       <c r="H6" t="n">
-        <v>390</v>
+        <v>420</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -27810,7 +27810,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>4590</v>
+        <v>6180</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -27819,13 +27819,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>4680</v>
+        <v>10950</v>
       </c>
       <c r="P6" t="n">
-        <v>5070</v>
+        <v>1290</v>
       </c>
       <c r="Q6" t="n">
-        <v>189.48</v>
+        <v>2638.35</v>
       </c>
     </row>
     <row r="7">
@@ -27851,7 +27851,7 @@
         <v>120</v>
       </c>
       <c r="H7" t="n">
-        <v>180</v>
+        <v>330</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -27863,7 +27863,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1440</v>
+        <v>3300</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -27872,13 +27872,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1440</v>
+        <v>3720</v>
       </c>
       <c r="P7" t="n">
-        <v>6090</v>
+        <v>4140</v>
       </c>
       <c r="Q7" t="n">
-        <v>31.92</v>
+        <v>444.51</v>
       </c>
     </row>
     <row r="8">
@@ -27904,7 +27904,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>60</v>
+        <v>330</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -27916,7 +27916,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>300</v>
+        <v>1680</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -27925,13 +27925,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>210</v>
+        <v>1260</v>
       </c>
       <c r="P8" t="n">
-        <v>4800</v>
+        <v>10440</v>
       </c>
       <c r="Q8" t="n">
-        <v>14.01</v>
+        <v>195.03</v>
       </c>
     </row>
     <row r="9">
@@ -27969,7 +27969,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>120</v>
+        <v>1680</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -27981,10 +27981,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2670</v>
+        <v>7020</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.7</v>
+        <v>51.48</v>
       </c>
     </row>
     <row r="10">
@@ -28010,7 +28010,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -28022,7 +28022,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>690</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -28034,10 +28034,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1110</v>
+        <v>3930</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.36</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="11">
@@ -28075,7 +28075,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -28087,10 +28087,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>150</v>
+        <v>630</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="12">
@@ -29037,7 +29037,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>658.8</v>
+        <v>1047.6</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -29049,7 +29049,7 @@
         <v>2.98</v>
       </c>
       <c r="L5" t="n">
-        <v>8996.4</v>
+        <v>11787.3</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -29058,13 +29058,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1078.5</v>
+        <v>1705.5</v>
       </c>
       <c r="P5" t="n">
-        <v>75.59999999999999</v>
+        <v>11.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>196.29</v>
+        <v>2733.19</v>
       </c>
     </row>
     <row r="6">
@@ -29090,7 +29090,7 @@
         <v>46.5</v>
       </c>
       <c r="H6" t="n">
-        <v>222.3</v>
+        <v>239.4</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -29102,7 +29102,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1698.3</v>
+        <v>2286.6</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -29111,13 +29111,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1170</v>
+        <v>2737.5</v>
       </c>
       <c r="P6" t="n">
-        <v>760.5</v>
+        <v>193.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>142.11</v>
+        <v>1978.76</v>
       </c>
     </row>
     <row r="7">
@@ -29143,7 +29143,7 @@
         <v>18</v>
       </c>
       <c r="H7" t="n">
-        <v>131.4</v>
+        <v>240.9</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -29155,7 +29155,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>864</v>
+        <v>1980</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -29164,13 +29164,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>504</v>
+        <v>1302</v>
       </c>
       <c r="P7" t="n">
-        <v>1522.5</v>
+        <v>1035</v>
       </c>
       <c r="Q7" t="n">
-        <v>25.54</v>
+        <v>355.61</v>
       </c>
     </row>
     <row r="8">
@@ -29196,7 +29196,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>51</v>
+        <v>280.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -29208,7 +29208,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>213</v>
+        <v>1192.8</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -29217,13 +29217,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>94.5</v>
+        <v>567</v>
       </c>
       <c r="P8" t="n">
-        <v>1824</v>
+        <v>3967.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>13.31</v>
+        <v>185.28</v>
       </c>
     </row>
     <row r="9">
@@ -29261,7 +29261,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>97.2</v>
+        <v>1360.8</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -29273,10 +29273,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1335</v>
+        <v>3510</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.59</v>
+        <v>49.94</v>
       </c>
     </row>
     <row r="10">
@@ -29302,7 +29302,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -29314,7 +29314,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>614.1</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -29326,10 +29326,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>943.5</v>
+        <v>3340.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.36</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="11">
@@ -29367,7 +29367,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -29379,10 +29379,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>135</v>
+        <v>567</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="12">
@@ -30329,7 +30329,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>3755160</v>
+        <v>5971320</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -30341,7 +30341,7 @@
         <v>144648.32</v>
       </c>
       <c r="L5" t="n">
-        <v>1619352</v>
+        <v>2121714</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -30350,13 +30350,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>183345</v>
+        <v>289935</v>
       </c>
       <c r="P5" t="n">
-        <v>4914</v>
+        <v>741</v>
       </c>
       <c r="Q5" t="n">
-        <v>117775.73</v>
+        <v>1639915.2</v>
       </c>
     </row>
     <row r="6">
@@ -30382,7 +30382,7 @@
         <v>2511</v>
       </c>
       <c r="H6" t="n">
-        <v>1267110</v>
+        <v>1364580</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -30394,7 +30394,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>305694</v>
+        <v>411588</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -30403,13 +30403,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>198900</v>
+        <v>465375</v>
       </c>
       <c r="P6" t="n">
-        <v>49432.5</v>
+        <v>12577.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>85266.67999999999</v>
+        <v>1187257.5</v>
       </c>
     </row>
     <row r="7">
@@ -30435,7 +30435,7 @@
         <v>972</v>
       </c>
       <c r="H7" t="n">
-        <v>748980</v>
+        <v>1373130</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -30447,7 +30447,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>155520</v>
+        <v>356400</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -30456,13 +30456,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>85680</v>
+        <v>221340</v>
       </c>
       <c r="P7" t="n">
-        <v>98962.5</v>
+        <v>67275</v>
       </c>
       <c r="Q7" t="n">
-        <v>15323.47</v>
+        <v>213364.8</v>
       </c>
     </row>
     <row r="8">
@@ -30488,7 +30488,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>290700</v>
+        <v>1598850</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>38340</v>
+        <v>214704</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -30509,13 +30509,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>16065</v>
+        <v>96390</v>
       </c>
       <c r="P8" t="n">
-        <v>118560</v>
+        <v>257868</v>
       </c>
       <c r="Q8" t="n">
-        <v>7983.82</v>
+        <v>111167.1</v>
       </c>
     </row>
     <row r="9">
@@ -30553,7 +30553,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>17496</v>
+        <v>244944</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -30565,10 +30565,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>86775</v>
+        <v>228150</v>
       </c>
       <c r="Q9" t="n">
-        <v>2151.77</v>
+        <v>29961.36</v>
       </c>
     </row>
     <row r="10">
@@ -30594,7 +30594,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>342000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -30606,7 +30606,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>110538</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -30618,10 +30618,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>61327.5</v>
+        <v>217132.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>213.3</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="11">
@@ -30659,7 +30659,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>21600</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -30671,10 +30671,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>8775</v>
+        <v>36855</v>
       </c>
       <c r="Q11" t="n">
-        <v>42.66</v>
+        <v>594</v>
       </c>
     </row>
     <row r="12">
